--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$F$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Roles &amp; glossary'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traceability'!$A$1:$C$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints'!$A$1:$B$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5168,7 +5168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Nautobot 3.2.4: a brand-new custom field drops values until it is saved a second time; the profile ↔ policy assignment endpoints 500 on POST (worked around); a location's description is limited to 255 characters.</t>
+          <t>IOS-XE appends a route-map entry's description over RESTCONF instead of replacing it: a description whose text changes (it used to carry the internet-breakout preference rank, which a re-home changes) leaves the old line on the router and Golden Config reports drift. Rendered descriptions are therefore stable per object; the rank lives in set local-preference, which the provider does replace. Suite 11 asserts one description per route-map entry.</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Golden Config compliance needs parseable backups: a multi-line banner breaks hier_config for that device.</t>
+          <t>Nautobot 3.2.4: a brand-new custom field drops values until it is saved a second time; the profile ↔ policy assignment endpoints 500 on POST (worked around); a location's description is limited to 255 characters.</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>VyOS static routes have no description leaf; the breakout uplink uses DHCP on the libvirt NAT network.</t>
+          <t>Golden Config compliance needs parseable backups: a multi-line banner breaks hier_config for that device.</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Pre-shared keys are kept in the intent (a git-tracked file in the lab); a production deployment would move them to a secret store — the portal already treats them as secrets everywhere else.</t>
+          <t>VyOS static routes have no description leaf; the breakout uplink uses DHCP on the libvirt NAT network.</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Customers are synthetic (deterministic fakes); the model, fields and filters are what a real CRM feed would fill.</t>
+          <t>Pre-shared keys are kept in the intent (a git-tracked file in the lab); a production deployment would move them to a secret store — the portal already treats them as secrets everywhere else.</t>
         </is>
       </c>
     </row>
@@ -5263,12 +5263,22 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
+          <t>Customers are synthetic (deterministic fakes); the model, fields and filters are what a real CRM feed would fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
           <t>Both labs on the host share one Nautobot and one NMS; their test suites must not run concurrently.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Constraints" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$F$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$F$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Roles &amp; glossary'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traceability'!$A$1:$C$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traceability'!$A$1:$C$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -770,14 +770,14 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Access control and audit</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>1</v>
@@ -789,14 +789,14 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Access control and audit</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>1</v>
@@ -808,17 +808,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="6" t="n">
         <v>0</v>
@@ -827,17 +827,17 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
         <v>8</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>0</v>
@@ -846,17 +846,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Monitoring and alerting</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
@@ -884,7 +884,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Verification (tests)</t>
+          <t>Monitoring and alerting</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -903,14 +903,14 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Lab infrastructure</t>
+          <t>Verification (tests)</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>1</v>
@@ -922,17 +922,17 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Lab infrastructure</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>0</v>
@@ -941,213 +941,232 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>106</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="E30" s="7" t="n">
+      <c r="B31" s="7" t="n">
+        <v>113</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" s="7" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>System context</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Responsibility</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Where</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Routers</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>3 C8000v headends (east / central / west), 4+ C8000v spokes (branches); IOS-XE 17.x, RESTCONF, SSH</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>libvirt VMs, OOB network 10.2.0.0/24</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Firewalls</t>
+          <t>Routers</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>one VyOS firewall in front of each headend: the spokes' WAN links land on it; forward-filter policy, NAT breakout, syslog</t>
+          <t>3 C8000v headends (east / central / west), 4+ C8000v spokes (branches); IOS-XE 17.x, RESTCONF, SSH</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>libvirt VMs</t>
+          <t>libvirt VMs, OOB network 10.2.0.0/24</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>LAN hosts</t>
+          <t>Firewalls</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>one Alpine Linux VM behind every router (its site LAN); the ping-mesh endpoints</t>
+          <t>one VyOS firewall in front of each headend: the spokes' WAN links land on it; forward-filter policy, NAT breakout, syslog</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>libvirt VMs, 256 MiB</t>
+          <t>libvirt VMs</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Nautobot 3.2 (+ bgp-models, golden-config, device-onboarding)</t>
+          <t>LAN hosts</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>source of truth: devices, interfaces, cables, prefixes, VPN app, BGP, tenants, custom fields, config contexts, Golden Config</t>
+          <t>one Alpine Linux VM behind every router (its site LAN); the ping-mesh endpoints</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>NMS VM 10.0.0.10 (shared with the SRv6 lab)</t>
+          <t>libvirt VMs, 256 MiB</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Gitea</t>
+          <t>Nautobot 3.2 (+ bgp-models, golden-config, device-onboarding)</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Golden Config backup / intended / template repositories; OIDC provider for the portal</t>
+          <t>source of truth: devices, interfaces, cables, prefixes, VPN app, BGP, tenants, custom fields, config contexts, Golden Config</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>NMS VM</t>
+          <t>NMS VM 10.0.0.10 (shared with the SRv6 lab)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Network-as-Code</t>
+          <t>Gitea</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>netascode/nac-iosxe module, CiscoDevNet/iosxe provider 0.15; data rendered from Nautobot</t>
+          <t>Golden Config backup / intended / template repositories; OIDC provider for the portal</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>nac/, Terraform state on the lab host</t>
+          <t>NMS VM</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Network-as-Code</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>FastAPI + single-page UI on :8090: provisioning, day-2 operations, inventory, branches, compliance, audit, metrics</t>
+          <t>netascode/nac-iosxe module, CiscoDevNet/iosxe provider 0.15; data rendered from Nautobot</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>lab host, systemd --user lab-webapp</t>
+          <t>nac/, Terraform state on the lab host</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Portal</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Prometheus, VictoriaMetrics, VictoriaLogs, vmalert, Grafana (lab-portal/monitoring)</t>
+          <t>FastAPI + single-page UI on :8090: provisioning, day-2 operations, inventory, branches, compliance, audit, metrics</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>NMS VM, Docker Compose</t>
+          <t>lab host, systemd --user lab-webapp</t>
         </is>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Prometheus, VictoriaMetrics, VictoriaLogs, vmalert, Grafana (lab-portal/monitoring)</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NMS VM, Docker Compose</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Robot Framework suites 01–11; results per run with config backups and diffs</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>tests/, results/</t>
         </is>
@@ -1171,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2234,7 +2253,7 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>suite 07 "The firewalls ship their firewall log…"; dashboard panels and log alerts (§17)</t>
+          <t>suite 07 "The firewalls ship their firewall log…"; dashboard panels and log alerts (§18)</t>
         </is>
       </c>
     </row>
@@ -2817,17 +2836,17 @@
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>SEC-01</t>
+          <t>DCI-01</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Access control and audit</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>12. Portal: access control, sign-in, audit</t>
+          <t>12. Data-centre interconnect: an acquired company, overlapping addresses, NAT and DNS</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -2837,29 +2856,29 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Roles viewer / operator / approver: reads need a viewer; writes an operator; removing a spoke and user management an approver; validation endpoints are open to viewers; a few read-only endpoints (metrics, pki, hosts, oidc) are open for the collectors and tests.</t>
+          <t>A data-centre interconnect hangs off one headend (west-headend Gi3 → DCI → ACME-acquisition) on plain routed /30s with no IPsec: ACME owns the DCI (tenant ACME Networks, role vpn-dci), the acquired company is a customer tenant of its own on a partner-edge router. Devices, cables, prefixes, peerings and tenants are modelled in Nautobot and rendered by the same NaC pipeline and Golden Config template as everything else.</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>auth.required_role; 401 / 403 with the required role; suite 10 checks role gates</t>
+          <t>suite 12 "The DCI chain is modelled in Nautobot…", "The interconnect links are up … no IPsec anywhere on them"</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>SEC-02</t>
+          <t>DCI-02</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Access control and audit</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>12. Portal: access control, sign-in, audit</t>
+          <t>12. Data-centre interconnect: an acquired company, overlapping addresses, NAT and DNS</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -2869,29 +2888,29 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Local users (salted scrypt hashes in users.json, CLI to add users, session cookie, bearer tokens for automation) and single sign-on via OpenID Connect (authorization code + PKCE, JWKS-verified ID token, provider groups → role; Gitea in the lab).</t>
+          <t>eBGP per hop (65206 ↔ 65208 ↔ 65209) from the same nautobot-bgp-models peerings the tunnels use; the acquisition originates its site LAN and a service prefix on a loopback, which every branch learns through one of its headends and can reach from its own LAN address; the host behind the acquisition joins the ping mesh and breaks out to the internet through the headend.</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>suite 10 "Single sign-on is offered…"; webapp/auth.py</t>
+          <t>suite 12 "eBGP is Established on every hop…", "The acquisition originates its prefixes…", "A branch reaches the acquisition's LAN…", "The host behind the acquisition is in the mesh…"</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>SEC-03</t>
+          <t>DCI-03</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Access control and audit</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>12. Portal: access control, sign-in, audit</t>
+          <t>12. Data-centre interconnect: an acquired company, overlapping addresses, NAT and DNS</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -2901,29 +2920,29 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Audit trail: every login (local / SSO / failed), run start / resume / cancel, write and denied request is recorded with user, role, source address, path, mode, spec (secrets redacted: a PSK becomes its fingerprint, passwords and tokens are dropped) and the run id; readable on the Audit tab and GET /api/audit with filters.</t>
+          <t>Overlapping address space is translated, not renumbered: the acquired company keeps a prefix ACME already uses (its own Nautobot namespace), and the DCI runs a twice-NAT — ip nat inside source static network (inside local → inside global) and ip nat outside source static network (outside global → outside local) — with ip nat inside / outside on the two interconnect ports. A prefix-list OVERLAP and route-map NO-OVERLAP filter the colliding prefix in and out towards ACME and out towards the acquisition, and the translated ranges are advertised instead (a Null0 route for the inside-global range, a route towards ACME for the outside-local one).</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>webapp/runs/audit.jsonl; suite 10</t>
+          <t>suite 12 "The overlapping prefix exists on both sides … neither side learns the other's copy", "The DCI translates in both directions…"</t>
         </is>
       </c>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>SEC-04</t>
+          <t>DCI-04</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Access control and audit</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>12. Portal: access control, sign-in, audit</t>
+          <t>12. Data-centre interconnect: an acquired company, overlapping addresses, NAT and DNS</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -2933,61 +2952,61 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>Secrets never reach Nautobot, the audit log or viewers' screens: router credentials come from environment / secrets group, PSKs appear only to operators, remediation lines and configurations are redacted for viewers.</t>
+          <t>DNS fix-up in both directions: each side answers for its own zone (ip dns server + ip host records rendered from the intent), the far side resolves through the DCI from an address the NAT translates, and the ALG rewrites the A records in flight so what a client resolves is what it can reach. A LAN host's resolver comes from the intent (dns_client, written by cloud-init; the instance-id follows a hash of the seed so a changed resolver is applied on the next boot).</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>branch_config redaction; Run.do_rem_validate log redaction</t>
+          <t>suite 12 "DNS is fixed up on the way through the NAT…", "DNS fix-up scales and works from either side…"</t>
         </is>
       </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>SEC-05</t>
+          <t>DCI-05</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Access control and audit</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>12. Portal: access control, sign-in, audit</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>12. Data-centre interconnect: an acquired company, overlapping addresses, NAT and DNS</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>The UI adapts to the role: buttons the user cannot use are disabled with the required role as tooltip; a 401 opens the sign-in dialog.</t>
+          <t>Scale: a scale block expands to 1000 overlapping /24s on both sides — 2002 static translations on the DCI — while BGP carries only three aggregates; each side holds its thousand addresses as secondary addresses on one loopback, and the renderer splits CLI templates into 400-line chunks (IOS-XE's CLI RPC rejects a larger payload). Each zone carries 1000 records over the same set.</t>
         </is>
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>applyRoles()</t>
+          <t>suite 12 "NAT scales: a thousand overlapping prefixes…" (reached 1000/1000, no drops, aggregates only) and "DNS fix-up scales…" (resolved+reached 1000/1000)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>RUN-01</t>
+          <t>DCI-06</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>12. Data-centre interconnect: an acquired company, overlapping addresses, NAT and DNS</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
@@ -2997,61 +3016,61 @@
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>Every change is an asynchronous run (POST /api/runs → id; GET /api/runs/{id} with incremental log) made of named steps with status, timing and a one-line summary; a run ends success / failed / cancelled / interrupted, carries a results directory and a parsed Robot test report when tests ran.</t>
+          <t>The NAT and the DNS are under configuration compliance like everything else: two Golden Config features (NAT (DCI), DNS) whose intended configuration is rendered from the same config context — including the full scale set — so a hand-edit anywhere in it shows up as drift.</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>suite 10; run records under webapp/runs/</t>
+          <t>171/171 compliance rows compliant; suite 12 "Golden Config renders the DCI chain…"</t>
         </is>
       </c>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>RUN-02</t>
+          <t>DCI-07</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Interconnect, NAT and DNS</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>12. Data-centre interconnect: an acquired company, overlapping addresses, NAT and DNS</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>Runs execute one at a time in the order started (one Terraform state, one intent); a queued run shows its place in line and the run it waits for and can be cancelled; a portal restart marks in-flight runs interrupted.</t>
+          <t>The interconnect is visible in the portal: the DCI and the acquisition appear on both topology views (dashed, as non-IPsec links) and in the Branches table with their tenant and design pattern.</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>suite 10 "runs queue instead of colliding…"; DELETE /api/runs/{id}</t>
+          <t>topology screenshots; suite 10 / suite 06</t>
         </is>
       </c>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>RUN-03</t>
+          <t>SEC-01</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Access control and audit</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>13. Portal: access control, sign-in, audit</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -3061,29 +3080,29 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>A failed or interrupted run can be resumed from the failed step, keeping the successful steps and the original starter; the resume is audited.</t>
+          <t>Roles viewer / operator / approver: reads need a viewer; writes an operator; removing a spoke and user management an approver; validation endpoints are open to viewers; a few read-only endpoints (metrics, pki, hosts, oidc) are open for the collectors and tests.</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>POST /api/runs/{id}/resume</t>
+          <t>auth.required_role; 401 / 403 with the required role; suite 10 checks role gates</t>
         </is>
       </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>RUN-04</t>
+          <t>SEC-02</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Access control and audit</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>13. Portal: access control, sign-in, audit</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -3093,29 +3112,29 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>deploy: validate → save intent → Nautobot seed → render → pki → firewalls → plan → staged apply → post-apply verification → Golden Config → tests (Golden Config and tests optional). plan: the same up to terraform plan, nothing pushed. test: the Robot suites only.</t>
+          <t>Local users (salted scrypt hashes in users.json, CLI to add users, session cookie, bearer tokens for automation) and single sign-on via OpenID Connect (authorization code + PKCE, JWKS-verified ID token, provider groups → role; Gitea in the lab).</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>Run.plan(); suites 05 / 06 / 10</t>
+          <t>suite 10 "Single sign-on is offered…"; webapp/auth.py</t>
         </is>
       </c>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>RUN-05</t>
+          <t>SEC-03</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Access control and audit</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>13. Portal: access control, sign-in, audit</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -3125,29 +3144,29 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>spoke: provision a new branch end to end — validate the allocation → register in lab.conf + day-0 config → create and boot the VM → bootstrap (day-0, license reload, RESTCONF) → onboard into Nautobot → add to the intent (links, tunnels, BGP, customer) → seed → render → pki → firewalls → plan → apply → verify → Golden Config → tests. Hub and spoke are configured in one Terraform run.</t>
+          <t>Audit trail: every login (local / SSO / failed), run start / resume / cancel, write and denied request is recorded with user, role, source address, path, mode, spec (secrets redacted: a PSK becomes its fingerprint, passwords and tokens are dropped) and the run id; readable on the Audit tab and GET /api/audit with filters.</t>
         </is>
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>wizard + GET /api/spokes/suggest, POST /api/spokes/validate; suite 10 exercises validation</t>
+          <t>webapp/runs/audit.jsonl; suite 10</t>
         </is>
       </c>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>RUN-06</t>
+          <t>SEC-04</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Access control and audit</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>13. Portal: access control, sign-in, audit</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
@@ -3157,51 +3176,51 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>hub: provision a new headend with a link and tunnel to every selected spoke, the same pipeline.</t>
+          <t>Secrets never reach Nautobot, the audit log or viewers' screens: router credentials come from environment / secrets group, PSKs appear only to operators, remediation lines and configurations are redacted for viewers.</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>GET /api/hubs/suggest, HubSpec</t>
+          <t>branch_config redaction; Run.do_rem_validate log redaction</t>
         </is>
       </c>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>RUN-07</t>
+          <t>SEC-05</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Runs and day-2 operations</t>
+          <t>Access control and audit</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>13. Portal: access control, sign-in, audit</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>remove (approver): show what is released and what each headend loses → power off → Nautobot clean-up (tunnel, endpoints, BGP, device, addresses, prefixes, AS, tenant) → intent and lab.conf → Terraform state → apply on the headends → delete the VM (disk optional) → Golden Config → tests.</t>
+          <t>The UI adapts to the role: buttons the user cannot use are disabled with the required role as tooltip; a 401 opens the sign-in dialog.</t>
         </is>
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>GET /api/spokes/{name}/removal; spokes.remove_*</t>
+          <t>applyRoles()</t>
         </is>
       </c>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>RUN-08</t>
+          <t>RUN-01</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -3211,7 +3230,7 @@
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -3221,19 +3240,19 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>rehome: change a running branch's set of headends (at least two): new links / tunnels allocated, the VM redefined and rebooted for the new NIC, dropped ones removed from intent, lab.conf and Nautobot, terraform on hubs and spoke, verification that new tunnels are READY + Established and dropped ones gone.</t>
+          <t>Every change is an asynchronous run (POST /api/runs → id; GET /api/runs/{id} with incremental log) made of named steps with status, timing and a one-line summary; a run ends success / failed / cancelled / interrupted, carries a results directory and a parsed Robot test report when tests ran.</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>GET /api/spokes/{name}/rehome; suite 10 branch actions</t>
+          <t>suite 10; run records under webapp/runs/</t>
         </is>
       </c>
     </row>
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>RUN-09</t>
+          <t>RUN-02</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -3243,7 +3262,7 @@
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
@@ -3253,19 +3272,19 @@
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>rotate (PSK), auth (PSK ↔ certificate), renew (certificate) as described in §8, each with a plan / preview endpoint the dialog shows before starting.</t>
+          <t>Runs execute one at a time in the order started (one Terraform state, one intent); a queued run shows its place in line and the run it waits for and can be cancelled; a portal restart marks in-flight runs interrupted.</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>suite 08 performs a real renewal and a real switch there and back</t>
+          <t>suite 10 "runs queue instead of colliding…"; DELETE /api/runs/{id}</t>
         </is>
       </c>
     </row>
     <row r="66" ht="58" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>RUN-10</t>
+          <t>RUN-03</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -3275,7 +3294,7 @@
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
@@ -3285,19 +3304,19 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>golden, remediate, reapply as described in §15.</t>
+          <t>A failed or interrupted run can be resumed from the failed step, keeping the successful steps and the original starter; the resume is audited.</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>suite 10 remediation tests</t>
+          <t>POST /api/runs/{id}/resume</t>
         </is>
       </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>RUN-11</t>
+          <t>RUN-04</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -3307,39 +3326,39 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>13. Portal: provisioning and day-2 operations (runs)</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>Every spec is validated before a run starts (422 with the list of problems) so a run never begins on bad input; suggestions (next free management IP, node index, ports, /30s, tunnel ids, router-id, LAN, AS, site, city, PSK, customer) are offered for every field.</t>
+          <t>deploy: validate → save intent → Nautobot seed → render → pki → firewalls → plan → staged apply → post-apply verification → Golden Config → tests (Golden Config and tests optional). plan: the same up to terraform plan, nothing pushed. test: the Robot suites only.</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>spokes.suggest / validate; suite 10</t>
+          <t>Run.plan(); suites 05 / 06 / 10</t>
         </is>
       </c>
     </row>
     <row r="68" ht="58" customHeight="1">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>UI-01</t>
+          <t>RUN-05</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -3349,29 +3368,29 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>Provision: the intent as a form (site, service, profile, crypto, PSK policy, internet breakout, capacity); the routers table with role, region, site, AS, router-id, LAN, IKE method, PSK (operators), certificate days left, comments, and the day-2 actions (Change auth, Rotate PSK, Renew cert, Re-home, Remove); Add spoke / Add headend wizards; Deploy / Dry run / Run tests; the run status panel (steps, log, test report) and the recent runs list.</t>
+          <t>spoke: provision a new branch end to end — validate the allocation → register in lab.conf + day-0 config → create and boot the VM → bootstrap (day-0, license reload, RESTCONF) → onboard into Nautobot → add to the intent (links, tunnels, BGP, customer) → seed → render → pki → firewalls → plan → apply → verify → Golden Config → tests. Hub and spoke are configured in one Terraform run.</t>
         </is>
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>screenshots and demo; suite 10</t>
+          <t>wizard + GET /api/spokes/suggest, POST /api/spokes/validate; suite 10 exercises validation</t>
         </is>
       </c>
     </row>
     <row r="69" ht="58" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>UI-02</t>
+          <t>RUN-06</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -3381,29 +3400,29 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>Add-spoke wizard: step 1 identity, metadata, city (catalogue with coordinates, or any name with lat / lon), IKE authentication, PSK, customer block, headends (≥ 2); step 2 auto-suggested addressing, editable and re-validated; step 3 the review of what happens on the spoke and on each headend (WAN ports, tunnels, neighbours, Nautobot objects, design pattern, capacity after) → Provision.</t>
+          <t>hub: provision a new headend with a link and tunnel to every selected spoke, the same pipeline.</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>SpokeSpec; hub_changes</t>
+          <t>GET /api/hubs/suggest, HubSpec</t>
         </is>
       </c>
     </row>
     <row r="70" ht="58" customHeight="1">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>UI-03</t>
+          <t>RUN-07</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
@@ -3413,29 +3432,29 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>Inventory: KPIs (Nautobot's VPN model joined with live IKEv2 / VTI / eBGP / ESP state from the headends), a rendered topology (headends on top, spokes below, one line per tunnel coloured by health, hover for details, click to open in Nautobot) and a map of the sites, headend capacity (tunnels, bandwidth, CPU / QFP / DRAM, the binding constraint), the per-tunnel report with CSV export, the LAN hosts and their ping mesh.</t>
+          <t>remove (approver): show what is released and what each headend loses → power off → Nautobot clean-up (tunnel, endpoints, BGP, device, addresses, prefixes, AS, tenant) → intent and lab.conf → Terraform state → apply on the headends → delete the VM (disk optional) → Golden Config → tests.</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>GET /api/vpn-inventory[.csv]; suite 07 "Headend CPU is collected live…"</t>
+          <t>GET /api/spokes/{name}/removal; spokes.remove_*</t>
         </is>
       </c>
     </row>
     <row r="71" ht="58" customHeight="1">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>UI-04</t>
+          <t>RUN-08</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
@@ -3445,29 +3464,29 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>Branches: every branch and headend with customer / owner, site and address, design pattern, tier, AS, LAN, VM state, tunnels up, IKE method, certificate, LAN host, free slots, last run; the filter bar of CUST-04; rows open the router's page.</t>
+          <t>rehome: change a running branch's set of headends (at least two): new links / tunnels allocated, the VM redefined and rebooted for the new NIC, dropped ones removed from intent, lab.conf and Nautobot, terraform on hubs and spoke, verification that new tunnels are READY + Established and dropped ones gone.</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>GET /api/branches; suite 10 "The Branches list…"</t>
+          <t>GET /api/spokes/{name}/rehome; suite 10 branch actions</t>
         </is>
       </c>
     </row>
     <row r="72" ht="58" customHeight="1">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>UI-05</t>
+          <t>RUN-09</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
@@ -3477,29 +3496,29 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>Router page (#branch/&lt;name&gt;): customer / owner box, identity (site, router-id, LAN, WAN addresses, firewall, internet preference), authentication and certificate with the day-2 actions, tunnels with live state (and a headend's capacity line), firewall rules / flows / log touching it, its LAN host, the runs that involved it, live show commands from an allow-list (IKE, IPsec, BGP, routes, default, interfaces, PKI, platform, log; other commands refused), and the configuration: running config over SSH (re-read, download), Nautobot's intended config and last backup, compliance per feature with a running-vs-intended diff, the Gitea backup history with per-commit diffs, a dark / light toggle for the code panes.</t>
+          <t>rotate (PSK), auth (PSK ↔ certificate), renew (certificate) as described in §8, each with a plan / preview endpoint the dialog shows before starting.</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>GET /api/branch/{name}[/config|/history|/show/{what}]; suite 10 "Every router has a page…", "…shows its configuration", "…history from Gitea"</t>
+          <t>suite 08 performs a real renewal and a real switch there and back</t>
         </is>
       </c>
     </row>
     <row r="73" ht="58" customHeight="1">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>UI-06</t>
+          <t>RUN-10</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -3509,29 +3528,29 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Firewalls, Compliance (§15), Audit (§12), Tools (every lab system with URL and login, how to reach each device), the REST API (Swagger / ReDoc) from the navigation.</t>
+          <t>golden, remediate, reapply as described in §16.</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>screenshots; suite 07 / 10</t>
+          <t>suite 10 remediation tests</t>
         </is>
       </c>
     </row>
     <row r="74" ht="58" customHeight="1">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>UI-07</t>
+          <t>RUN-11</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Portal pages</t>
+          <t>Runs and day-2 operations</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
+          <t>14. Portal: provisioning and day-2 operations (runs)</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -3541,19 +3560,19 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>Dark mode for the whole portal (CSS tokens; follows the OS setting until chosen; header toggle; remembered per browser).</t>
+          <t>Every spec is validated before a run starts (422 with the list of problems) so a run never begins on bad input; suggestions (next free management IP, node index, ports, /30s, tunnel ids, router-id, LAN, AS, site, city, PSK, customer) are offered for every field.</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>screenshot portal-dark.png</t>
+          <t>spokes.suggest / validate; suite 10</t>
         </is>
       </c>
     </row>
     <row r="75" ht="58" customHeight="1">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>UI-08</t>
+          <t>UI-01</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -3563,39 +3582,39 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>14. Portal: pages</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>15. Portal: pages</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Every router name anywhere (tables, tunnels, compliance, history) links to its page; Nautobot objects link to Nautobot; the header shows the signed-in user and role.</t>
+          <t>Provision: the intent as a form (site, service, profile, crypto, PSK policy, internet breakout, capacity); the routers table with role, region, site, AS, router-id, LAN, IKE method, PSK (operators), certificate days left, comments, and the day-2 actions (Change auth, Rotate PSK, Renew cert, Re-home, Remove); Add spoke / Add headend wizards; Deploy / Dry run / Run tests; the run status panel (steps, log, test report) and the recent runs list.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>branchLink()</t>
+          <t>screenshots and demo; suite 10</t>
         </is>
       </c>
     </row>
     <row r="76" ht="58" customHeight="1">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>CMP-01</t>
+          <t>UI-02</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
+          <t>15. Portal: pages</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
@@ -3605,29 +3624,29 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>The Compliance page shows Nautobot Golden Config's verdict: one row per router, one column per feature (✓ / ✕), KPIs (routers and rows compliant, features, last run, schedule), each device's last backup / intended / compliance dates; a cell shows the missing and extra lines, Nautobot's remediation lines and a running-vs-intended diff; non-compliant rows are listed and the first opened.</t>
+          <t>Add-spoke wizard: step 1 identity, metadata, city (catalogue with coordinates, or any name with lat / lon), IKE authentication, PSK, customer block, headends (≥ 2); step 2 auto-suggested addressing, editable and re-validated; step 3 the review of what happens on the spoke and on each headend (WAN ports, tunnels, neighbours, Nautobot objects, design pattern, capacity after) → Provision.</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>GET /api/compliance (cached 30 s, ?refresh); suite 10 "The Compliance page…"</t>
+          <t>SpokeSpec; hub_changes</t>
         </is>
       </c>
     </row>
     <row r="77" ht="58" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>CMP-02</t>
+          <t>UI-03</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
+          <t>15. Portal: pages</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
@@ -3637,29 +3656,29 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Run Golden Config now (operator): backup every router → render the intended configuration → compliance, nothing pushed; the run fails when any row is non-compliant (so drift is visible as a failed run) and refreshes the report at its end.</t>
+          <t>Inventory: KPIs (Nautobot's VPN model joined with live IKEv2 / VTI / eBGP / ESP state from the headends), a rendered topology (headends on top, spokes below, one line per tunnel coloured by health, hover for details, click to open in Nautobot) and a map of the sites, headend capacity (tunnels, bandwidth, CPU / QFP / DRAM, the binding constraint), the per-tunnel report with CSV export, the LAN hosts and their ping mesh.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>run mode golden; suite 10</t>
+          <t>GET /api/vpn-inventory[.csv]; suite 07 "Headend CPU is collected live…"</t>
         </is>
       </c>
     </row>
     <row r="78" ht="58" customHeight="1">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>CMP-03</t>
+          <t>UI-04</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
+          <t>15. Portal: pages</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -3669,29 +3688,29 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Remediate (operator): for a router's non-compliant features (one, or all), read the verdict again, push the remediation lines Nautobot computed (hier_config: no … for what is extra, the missing lines themselves) in one configuration session, fail on any rejected line, save the configuration, then run Golden Config; refuse a compliant router or a feature without remediation lines.</t>
+          <t>Branches: every branch and headend with customer / owner, site and address, design pattern, tier, AS, LAN, VM state, tunnels up, IKE method, certificate, LAN host, free slots, last run; the filter bar of CUST-04; rows open the router's page.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>run mode remediate; suite 10 "Drift on a router is detected…, remediated…"</t>
+          <t>GET /api/branches; suite 10 "The Branches list…"</t>
         </is>
       </c>
     </row>
     <row r="79" ht="58" customHeight="1">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>CMP-04</t>
+          <t>UI-05</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
+          <t>15. Portal: pages</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
@@ -3701,29 +3720,29 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>Re-apply from the model (operator): re-assert the model on one router — NaC render → Terraform plan filtered to the router's resources → staged apply targeted at them (skipped when clean) → Golden Config.</t>
+          <t>Router page (#branch/&lt;name&gt;): customer / owner box, identity (site, router-id, LAN, WAN addresses, firewall, internet preference), authentication and certificate with the day-2 actions, tunnels with live state (and a headend's capacity line), firewall rules / flows / log touching it, its LAN host, the runs that involved it, live show commands from an allow-list (IKE, IPsec, BGP, routes, default, interfaces, PKI, platform, log; other commands refused), and the configuration: running config over SSH (re-read, download), Nautobot's intended config and last backup, compliance per feature with a running-vs-intended diff, the Gitea backup history with per-commit diffs, a dark / light toggle for the code panes.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>run mode reapply, nac_apply.py --device; suite 10 "Re-apply from the model restores…"</t>
+          <t>GET /api/branch/{name}[/config|/history|/show/{what}]; suite 10 "Every router has a page…", "…shows its configuration", "…history from Gitea"</t>
         </is>
       </c>
     </row>
     <row r="80" ht="58" customHeight="1">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>CMP-05</t>
+          <t>UI-06</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
+          <t>15. Portal: pages</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -3733,83 +3752,83 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>A scheduled Golden Config run every GOLDEN_INTERVAL_HOURS (default 6; 0 disables), queued as the audited user scheduler, first due one interval after Nautobot's last compliance run (at the earliest two minutes after start-up), skipped and retried while another run is going or the headends are off; interval, next and last run exposed on the page and the API.</t>
+          <t>Firewalls, Compliance (§16), Audit (§13), Tools (every lab system with URL and login, how to reach each device), the REST API (Swagger / ReDoc) from the navigation.</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>golden_schedule(); suite 10 asserts the schedule is enabled and in the future</t>
+          <t>screenshots; suite 07 / 10</t>
         </is>
       </c>
     </row>
     <row r="81" ht="58" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>CMP-06</t>
+          <t>UI-07</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>15. Portal: pages</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Drift history: one snapshot per compliance run (per router: compliant, rows, drifted features) appended to compliance-history.jsonl whenever a new compliance date appears; the last 30 shown as dots per router and as a table (which routers drifted, when fixed); per-router series on its page and at GET /api/compliance/history?device=.</t>
+          <t>Dark mode for the whole portal (CSS tokens; follows the OS setting until chosen; header toggle; remembered per browser).</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>suite 10 checks the drift and its repair appear in the history</t>
+          <t>screenshot portal-dark.png</t>
         </is>
       </c>
     </row>
     <row r="82" ht="58" customHeight="1">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>CMP-07</t>
+          <t>UI-08</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>15. Portal: pages</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Compliance is exported to Prometheus (lab_config_compliance_ok{device}, lab_config_noncompliant_features, lab_config_compliance_features, lab_config_compliance_last_run_timestamp_seconds, lab_config_compliance_interval_seconds, lab_config_compliance_error) with alerts ConfigDrift (non-compliant 10 min) and ConfigComplianceStale (no run for twice the interval while the lab is up) and a dashboard row.</t>
+          <t>Every router name anywhere (tables, tunnels, compliance, history) links to its page; Nautobot objects link to Nautobot; the header shows the signed-in user and role.</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>suite 10 reads the metric before and after remediation; lab-portal alerts.yml</t>
+          <t>branchLink()</t>
         </is>
       </c>
     </row>
     <row r="83" ht="58" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>CMP-08</t>
+          <t>CMP-01</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -3819,7 +3838,7 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>15. Configuration compliance, remediation, scheduling and drift history</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -3829,29 +3848,29 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>Terraform-level compliance: after a deploy terraform plan reports no drift from the NaC data model.</t>
+          <t>The Compliance page shows Nautobot Golden Config's verdict: one row per router, one column per feature (✓ / ✕), KPIs (routers and rows compliant, features, last run, schedule), each device's last backup / intended / compliance dates; a cell shows the missing and extra lines, Nautobot's remediation lines and a running-vs-intended diff; non-compliant rows are listed and the first opened.</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>suite 05</t>
+          <t>GET /api/compliance (cached 30 s, ?refresh); suite 10 "The Compliance page…"</t>
         </is>
       </c>
     </row>
     <row r="84" ht="58" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>API-01</t>
+          <t>CMP-02</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>16. REST API</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -3861,29 +3880,29 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Everything the UI does is available as a documented REST API (OpenAPI 3.1 at /openapi.json, Swagger UI at /docs, ReDoc at /redoc) with Pydantic schemas and examples; the UI uses nothing else.</t>
+          <t>Run Golden Config now (operator): backup every router → render the intended configuration → compliance, nothing pushed; the run fails when any row is non-compliant (so drift is visible as a failed run) and refreshes the report at its end.</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>tags intent, provisioning, runs, inventory, monitoring; suite 10 uses the API throughout</t>
+          <t>run mode golden; suite 10</t>
         </is>
       </c>
     </row>
     <row r="85" ht="58" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>API-02</t>
+          <t>CMP-03</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>16. REST API</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
@@ -3893,29 +3912,29 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Endpoints: /api/intent, /api/validate, /api/inventory; /api/spokes/suggest, /api/spokes/validate, /api/hubs/suggest, /api/cities, /api/spokes/{name}/removal|rehome|rotation|auth, /api/routers/{name}/renewal; /api/runs (list, start, get with since, resume, cancel); /api/vpn-inventory[.csv], /api/branches, /api/branch/{name}[/config|/history|/show/{what}], /api/firewalls, /api/hosts, /api/pki, /api/compliance[/history], /api/tools, /api/sd; /api/login|logout|me|oidc*, /api/users, /api/audit; /metrics.</t>
+          <t>Remediate (operator): for a router's non-compliant features (one, or all), read the verdict again, push the remediation lines Nautobot computed (hier_config: no … for what is extra, the missing lines themselves) in one configuration session, fail on any rejected line, save the configuration, then run Golden Config; refuse a compliant router or a feature without remediation lines.</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>webapp/app.py</t>
+          <t>run mode remediate; suite 10 "Drift on a router is detected…, remediated…"</t>
         </is>
       </c>
     </row>
     <row r="86" ht="58" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>API-03</t>
+          <t>CMP-04</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>16. REST API</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
@@ -3925,61 +3944,61 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Errors are explicit: 400 for an unknown mode, 401 / 403 with the required role, 404 for unknown routers / runs, 409 when a run cannot start, 422 with the list of problems for an invalid spec, 502 when a backing system (Gitea, Nautobot) fails.</t>
+          <t>Re-apply from the model (operator): re-assert the model on one router — NaC render → Terraform plan filtered to the router's resources → staged apply targeted at them (skipped when clean) → Golden Config.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>suite 10 asserts 404 / 422 / 4xx cases</t>
+          <t>run mode reapply, nac_apply.py --device; suite 10 "Re-apply from the model restores…"</t>
         </is>
       </c>
     </row>
     <row r="87" ht="58" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>API-04</t>
+          <t>CMP-05</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>16. REST API</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>Expensive reads are cached with an explicit refresh (inventory live state, firewalls, configuration 60 s, show commands 20 s, compliance 30 s, host mesh 60 s / live 3 s) and report when they were generated.</t>
+          <t>A scheduled Golden Config run every GOLDEN_INTERVAL_HOURS (default 6; 0 disables), queued as the audited user scheduler, first due one interval after Nautobot's last compliance run (at the earliest two minutes after start-up), skipped and retried while another run is going or the headends are off; interval, next and last run exposed on the page and the API.</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>generated field on the responses</t>
+          <t>golden_schedule(); suite 10 asserts the schedule is enabled and in the future</t>
         </is>
       </c>
     </row>
     <row r="88" ht="58" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>MON-01</t>
+          <t>CMP-06</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Monitoring and alerting</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>17. Monitoring, metrics and alerting</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
@@ -3989,29 +4008,29 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>The portal exposes /metrics: VMs running per node / role, per-tunnel health (2 up / 1 degraded / 0 down), IKE SA age, BGP prefixes, ESP counters and errors, VTI rates; per-headend tunnels / capacity / free slots / utilisation / CPU / QFP / DRAM / IKE sessions / bandwidth; certificate expiry and authentication per spoke; compliance (§15); run outcomes; collection errors.</t>
+          <t>Drift history: one snapshot per compliance run (per router: compliant, rows, drifted features) appended to compliance-history.jsonl whenever a new compliance date appears; the last 30 shown as dots per router and as a table (which routers drifted, when fixed); per-router series on its page and at GET /api/compliance/history?device=.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>Prometheus scrapes the portal; dashboard cat8000v-ipsec-overview</t>
+          <t>suite 10 checks the drift and its repair appear in the history</t>
         </is>
       </c>
     </row>
     <row r="89" ht="58" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>MON-02</t>
+          <t>CMP-07</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Monitoring and alerting</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>17. Monitoring, metrics and alerting</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -4021,29 +4040,29 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Alerts in the shared monitoring: TunnelDown, HeadendUnreachable, HeadendCapacityExhausted, HeadendCpuHigh, InternetBreakoutDown, CertificateExpiringSoon / CertificateExpired, ConfigDrift / ConfigComplianceStale, LabTestsFailed, PortalDown, and from the firewall log FirewallDropBurst / FirewallDroppingPeerTraffic.</t>
+          <t>Compliance is exported to Prometheus (lab_config_compliance_ok{device}, lab_config_noncompliant_features, lab_config_compliance_features, lab_config_compliance_last_run_timestamp_seconds, lab_config_compliance_interval_seconds, lab_config_compliance_error) with alerts ConfigDrift (non-compliant 10 min) and ConfigComplianceStale (no run for twice the interval while the lab is up) and a dashboard row.</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>lab-portal/monitoring/prometheus/alerts.yml, vmalert/logs-alerts.yml</t>
+          <t>suite 10 reads the metric before and after remediation; lab-portal alerts.yml</t>
         </is>
       </c>
     </row>
     <row r="90" ht="58" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>MON-03</t>
+          <t>CMP-08</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Monitoring and alerting</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>17. Monitoring, metrics and alerting</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
@@ -4053,61 +4072,61 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Firewall syslog lands in VictoriaLogs; the dashboard shows drops / accepts per firewall, drops by source, top dropped flows and the raw log; the portal queries the same store for the Firewalls page and a router's page.</t>
+          <t>Terraform-level compliance: after a deploy terraform plan reports no drift from the NaC data model.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>suite 07 "The firewalls ship their firewall log to VictoriaLogs, and the portal…"</t>
+          <t>suite 05</t>
         </is>
       </c>
     </row>
     <row r="91" ht="58" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>MON-04</t>
+          <t>API-01</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Monitoring and alerting</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>17. Monitoring, metrics and alerting</t>
-        </is>
-      </c>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>17. REST API</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Alerts only fire for a running lab (gated on the VM-running metric) so a powered-off lab is a normal state; dashboards are generated from code (gen_dashboards.py) and deployed with one script.</t>
+          <t>Everything the UI does is available as a documented REST API (OpenAPI 3.1 at /openapi.json, Swagger UI at /docs, ReDoc at /redoc) with Pydantic schemas and examples; the UI uses nothing else.</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>monitoring/deploy.sh</t>
+          <t>tags intent, provisioning, runs, inventory, monitoring; suite 10 uses the API throughout</t>
         </is>
       </c>
     </row>
     <row r="92" ht="58" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>TST-01</t>
+          <t>API-02</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Verification (tests)</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>18. Verification: the Robot Framework suites</t>
+          <t>17. REST API</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
@@ -4117,29 +4136,29 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet — 60 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
+          <t>Endpoints: /api/intent, /api/validate, /api/inventory; /api/spokes/suggest, /api/spokes/validate, /api/hubs/suggest, /api/cities, /api/spokes/{name}/removal|rehome|rotation|auth, /api/routers/{name}/renewal; /api/runs (list, start, get with since, resume, cancel); /api/vpn-inventory[.csv], /api/branches, /api/branch/{name}[/config|/history|/show/{what}], /api/firewalls, /api/hosts, /api/pki, /api/compliance[/history], /api/tools, /api/sd; /api/login|logout|me|oidc*, /api/users, /api/audit; /metrics.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>./lab.sh test; tests/resources/lab_vars.py</t>
+          <t>webapp/app.py</t>
         </is>
       </c>
     </row>
     <row r="93" ht="58" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>TST-02</t>
+          <t>API-03</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Verification (tests)</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>18. Verification: the Robot Framework suites</t>
+          <t>17. REST API</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -4149,93 +4168,93 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Tests that change the lab do so for real and leave it as found: a renewal, a PSK ↔ certificate switch there and back, injected drift remediated and re-applied, queued runs cancelled — with teardowns.</t>
+          <t>Errors are explicit: 400 for an unknown mode, 401 / 403 with the required role, 404 for unknown routers / runs, 409 when a run cannot start, 422 with the list of problems for an invalid spec, 502 when a backing system (Gitea, Nautobot) fails.</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>suites 08 and 10</t>
+          <t>suite 10 asserts 404 / 422 / 4xx cases</t>
         </is>
       </c>
     </row>
     <row r="94" ht="58" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>TST-03</t>
+          <t>API-04</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Verification (tests)</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>18. Verification: the Robot Framework suites</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>17. REST API</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate.</t>
+          <t>Expensive reads are cached with an explicit refresh (inventory live state, firewalls, configuration 60 s, show commands 20 s, compliance 30 s, host mesh 60 s / live 3 s) and report when they were generated.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>tests/run.sh, capture_configs.py</t>
+          <t>generated field on the responses</t>
         </is>
       </c>
     </row>
     <row r="95" ht="58" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>TST-04</t>
+          <t>MON-01</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Verification (tests)</t>
+          <t>Monitoring and alerting</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>18. Verification: the Robot Framework suites</t>
-        </is>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>18. Monitoring, metrics and alerting</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>Tests can be run from the portal (a test run, or at the end of any pipeline) and their report is parsed into the run (suites, tests, pass / fail, elapsed).</t>
+          <t>The portal exposes /metrics: VMs running per node / role, per-tunnel health (2 up / 1 degraded / 0 down), IKE SA age, BGP prefixes, ESP counters and errors, VTI rates; per-headend tunnels / capacity / free slots / utilisation / CPU / QFP / DRAM / IKE sessions / bandwidth; certificate expiry and authentication per spoke; compliance (§16); run outcomes; collection errors.</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>parse_robot; Run.tests</t>
+          <t>Prometheus scrapes the portal; dashboard cat8000v-ipsec-overview</t>
         </is>
       </c>
     </row>
     <row r="96" ht="58" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>LAB-01</t>
+          <t>MON-02</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Lab infrastructure</t>
+          <t>Monitoring and alerting</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>19. Lab infrastructure and operations</t>
+          <t>18. Monitoring, metrics and alerting</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -4245,29 +4264,29 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>lab.sh is the one operations entry point: up | down | status | console | ssh | bootstrap | wait | log | nac | nautobot (onboard | seed | render | vyos | pki | golden | token) | test | intent | webapp | rename | rebuild | clean | hosts; VMs are libvirt domains generated from lab.conf (node index → MACs, UDP socket links, console ports), with day-0 ISOs, license reload and RESTCONF wait on first boot.</t>
+          <t>Alerts in the shared monitoring: TunnelDown, HeadendUnreachable, HeadendCapacityExhausted, HeadendCpuHigh, InternetBreakoutDown, CertificateExpiringSoon / CertificateExpired, ConfigDrift / ConfigComplianceStale, LabTestsFailed, PortalDown, and from the firewall log FirewallDropBurst / FirewallDroppingPeerTraffic.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>README quick start</t>
+          <t>lab-portal/monitoring/prometheus/alerts.yml, vmalert/logs-alerts.yml</t>
         </is>
       </c>
     </row>
     <row r="97" ht="58" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>LAB-02</t>
+          <t>MON-03</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Lab infrastructure</t>
+          <t>Monitoring and alerting</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>19. Lab infrastructure and operations</t>
+          <t>18. Monitoring, metrics and alerting</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
@@ -4277,29 +4296,29 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>New routers, firewalls and hosts can be added without editing XML: the portal registers them in lab.conf, writes the day-0 config, defines and boots the VM; a spoke can be re-defined for a new NIC (re-home) and removed with its disk.</t>
+          <t>Firewall syslog lands in VictoriaLogs; the dashboard shows drops / accepts per firewall, drops by source, top dropped flows and the raw log; the portal queries the same store for the Firewalls page and a router's page.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>spokes.add_to_lab_conf / write_day0 / destroy_vm</t>
+          <t>suite 07 "The firewalls ship their firewall log to VictoriaLogs, and the portal…"</t>
         </is>
       </c>
     </row>
     <row r="98" ht="58" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>LAB-03</t>
+          <t>MON-04</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Lab infrastructure</t>
+          <t>Monitoring and alerting</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>19. Lab infrastructure and operations</t>
+          <t>18. Monitoring, metrics and alerting</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -4309,29 +4328,29 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>The portal runs as a user systemd service, the monitoring as Docker Compose on the NMS with one deploy script; both labs on the host never run their test suites concurrently.</t>
+          <t>Alerts only fire for a running lab (gated on the VM-running metric) so a powered-off lab is a normal state; dashboards are generated from code (gen_dashboards.py) and deployed with one script.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>lab-webapp.service, monitoring/deploy.sh</t>
+          <t>monitoring/deploy.sh</t>
         </is>
       </c>
     </row>
     <row r="99" ht="58" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>DOC-01</t>
+          <t>TST-01</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Verification (tests)</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>20. Documentation and demos</t>
+          <t>19. Verification: the Robot Framework suites</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -4341,29 +4360,29 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>A README describing the topology, quick start, every portal feature with screenshots, the Nautobot model, the pipeline, the test suites and the file map; component READMEs for the portal, Nautobot scripts, NaC, tests and monitoring.</t>
+          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet, 12 the DCI chain (incl. the twice-NAT and the DNS fix-up at scale) — 74 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>README.md, webapp/README.md, nautobot/README.md, …</t>
+          <t>./lab.sh test; tests/resources/lab_vars.py</t>
         </is>
       </c>
     </row>
     <row r="100" ht="58" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>DOC-02</t>
+          <t>TST-02</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Verification (tests)</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>20. Documentation and demos</t>
+          <t>19. Verification: the Robot Framework suites</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
@@ -4373,29 +4392,29 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Generated documents kept current from the code: the workflows / data-flow / decision-tree PDF, this requirements specification, the screenshots (docs/screenshots.py) and an annotated demo video of the portal (webapp/demo/record.py, MP4 + GIF) plus a Nautobot / NaC data-flow demo.</t>
+          <t>Tests that change the lab do so for real and leave it as found: a renewal, a PSK ↔ certificate switch there and back, injected drift remediated and re-applied, queued runs cancelled — with teardowns.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>docs/workflows.pdf, docs/requirements.pdf, webapp/demo/</t>
+          <t>suites 08 and 10</t>
         </is>
       </c>
     </row>
     <row r="101" ht="58" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>NFR-01</t>
+          <t>TST-03</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Verification (tests)</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>21. Non-functional requirements</t>
+          <t>19. Verification: the Robot Framework suites</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
@@ -4405,61 +4424,61 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Idempotence: seed, render, firewall push, pki and apply can be re-run at any time and change nothing when nothing changed.</t>
+          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate. Every run also produces report.pdf — an evidence report built from output.xml (tests/report_pdf.py): every suite and test with its result, its duration and the numbers it measured.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>seed "0 changes", render --check, vyos --check, pki --check, plan exit code 0</t>
+          <t>tests/run.sh, capture_configs.py</t>
         </is>
       </c>
     </row>
     <row r="102" ht="58" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>NFR-02</t>
+          <t>TST-04</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Verification (tests)</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>21. Non-functional requirements</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>19. Verification: the Robot Framework suites</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Safety of change: nothing is pushed without a plan; applies are staged; verification steps fail the run rather than leave a half-authenticated tunnel; a run never starts on an invalid spec; runs are serialised.</t>
+          <t>Tests can be run from the portal (a test run, or at the end of any pipeline) and their report is parsed into the run (suites, tests, pass / fail, elapsed).</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>§6, §8, §13</t>
+          <t>parse_robot; Run.tests</t>
         </is>
       </c>
     </row>
     <row r="103" ht="58" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>NFR-03</t>
+          <t>LAB-01</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Lab infrastructure</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>21. Non-functional requirements</t>
+          <t>20. Lab infrastructure and operations</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
@@ -4469,61 +4488,61 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Traceability: every change carries a change ticket, a user and a run id; Nautobot records fingerprints, certificates, dates; Gitea holds every backup; the audit log every action; results directories every test run.</t>
+          <t>lab.sh is the one operations entry point: up | down | status | console | ssh | bootstrap | wait | log | nac | nautobot (onboard | seed | render | vyos | pki | golden | token) | test | intent | webapp | rename | rebuild | clean | hosts; VMs are libvirt domains generated from lab.conf (node index → MACs, UDP socket links, console ports), with day-0 ISOs, license reload and RESTCONF wait on first boot.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>§12, §18</t>
+          <t>README quick start</t>
         </is>
       </c>
     </row>
     <row r="104" ht="58" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>LAB-02</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Lab infrastructure</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>21. Non-functional requirements</t>
-        </is>
-      </c>
-      <c r="D104" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>20. Lab infrastructure and operations</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>Responsiveness: pages render from caches within a second; a Golden Config run completes in about 20 s for 7 routers; a remediation in about 30 s; a re-apply in about 2 min; a spoke provisioning in about 15 min; the full test suite in about 45 min.</t>
+          <t>New routers, firewalls and hosts can be added without editing XML: the portal registers them in lab.conf, writes the day-0 config, defines and boots the VM; a spoke can be re-defined for a new NIC (re-home) and removed with its disk.</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>observed run timings in the run records</t>
+          <t>spokes.add_to_lab_conf / write_day0 / destroy_vm</t>
         </is>
       </c>
     </row>
     <row r="105" ht="58" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>NFR-05</t>
+          <t>LAB-03</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Lab infrastructure</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>21. Non-functional requirements</t>
+          <t>20. Lab infrastructure and operations</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -4533,81 +4552,305 @@
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>Resilience: the portal survives Nautobot / Gitea / headend outages on read paths (errors reported in place, collectors degrade, metrics export an error series); interrupted runs are marked and resumable.</t>
+          <t>The portal runs as a user systemd service, the monitoring as Docker Compose on the NMS with one deploy script; both labs on the host never run their test suites concurrently.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>inventory_error, lab_inventory_error, lab_config_compliance_error</t>
+          <t>lab-webapp.service, monitoring/deploy.sh</t>
         </is>
       </c>
     </row>
     <row r="106" ht="58" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>NFR-06</t>
+          <t>DOC-01</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>21. Non-functional requirements</t>
-        </is>
-      </c>
-      <c r="D106" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+          <t>21. Documentation and demos</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>Footprint: LAN hosts are 256 MiB VMs; routers 4 GiB; the whole lab fits one 57 GiB host next to the SRv6 lab and the NMS.</t>
+          <t>A README describing the topology, quick start, every portal feature with screenshots, the Nautobot model, the pipeline, the test suites and the file map; component READMEs for the portal, Nautobot scripts, NaC, tests and monitoring.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>memory check in spokes.validate before a VM is created</t>
+          <t>README.md, webapp/README.md, nautobot/README.md, …</t>
         </is>
       </c>
     </row>
     <row r="107" ht="58" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
+          <t>DOC-02</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>21. Documentation and demos</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>Generated documents kept current from the code: the workflows / data-flow / decision-tree PDF, this requirements specification, the screenshots (docs/screenshots.py) and an annotated demo video of the portal (webapp/demo/record.py, MP4 + GIF) plus a Nautobot / NaC data-flow demo.</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>docs/workflows.pdf, docs/requirements.pdf, webapp/demo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="58" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>NFR-01</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>Idempotence: seed, render, firewall push, pki and apply can be re-run at any time and change nothing when nothing changed.</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>seed "0 changes", render --check, vyos --check, pki --check, plan exit code 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="58" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>NFR-02</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>Safety of change: nothing is pushed without a plan; applies are staged; verification steps fail the run rather than leave a half-authenticated tunnel; a run never starts on an invalid spec; runs are serialised.</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>§6, §8, §14</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="58" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>NFR-03</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>Traceability: every change carries a change ticket, a user and a run id; Nautobot records fingerprints, certificates, dates; Gitea holds every backup; the audit log every action; results directories every test run.</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>§13, §19</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="58" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>NFR-04</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Responsiveness: pages render from caches within a second; a Golden Config run completes in about 20 s for 7 routers; a remediation in about 30 s; a re-apply in about 2 min; a run that renders, plans and applies the whole model (a spoke provisioning, an authentication switch) in about 12 min with the DCI's scale set in it; the full test suite in about 55 min.</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>observed run timings in the run records</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="58" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>NFR-05</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>Resilience: the portal survives Nautobot / Gitea / headend outages on read paths (errors reported in place, collectors degrade, metrics export an error series); interrupted runs are marked and resumable.</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>inventory_error, lab_inventory_error, lab_config_compliance_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="58" customHeight="1">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>NFR-06</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>Footprint: LAN hosts are 256 MiB VMs; routers 4 GiB; the whole lab fits one 57 GiB host next to the SRv6 lab and the NMS.</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>memory check in spokes.validate before a VM is created</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="58" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
           <t>NFR-07</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="B114" s="9" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
-        <is>
-          <t>21. Non-functional requirements</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
         <is>
           <t>SHOULD</t>
         </is>
       </c>
-      <c r="E107" s="9" t="inlineStr">
+      <c r="E114" s="9" t="inlineStr">
         <is>
           <t>Usability: every value the wizard needs is suggested; every dialog previews what will change; every table links to the object's page and to Nautobot; dark mode; the UI degrades to the role.</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
-        <is>
-          <t>§13, §14</t>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>§14, §15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F107"/>
+  <autoFilter ref="A1:F114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4859,7 +5102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5006,158 +5249,175 @@
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Hosts (HOST)</t>
+          <t>Interconnect, NAT and DNS (DCI)</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>tools/host_cmd.py, lab.sh hosts, webapp/app.py (lan_hosts)</t>
+          <t>nautobot/intent.py (nat, dns, dns_client, nat_scale), render_nac.py (templates, chunking), the Golden Config template, seed.py (namespace, tenants, peerings)</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>suite 09</t>
+          <t>suite 12</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Internet (INET)</t>
+          <t>Hosts (HOST)</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>render_vyos.py, render_nac.py, config context internet</t>
+          <t>tools/host_cmd.py, lab.sh hosts, webapp/app.py (lan_hosts)</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>suite 11</t>
+          <t>suite 09</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Security (SEC)</t>
+          <t>Internet (INET)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>webapp/auth.py, middleware in app.py</t>
+          <t>render_vyos.py, render_nac.py, config context internet</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>suite 10</t>
+          <t>suite 11</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Runs (RUN)</t>
+          <t>Security (SEC)</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>webapp/app.py (Run, run modes), labportal (RunRegistry), webapp/spokes.py</t>
+          <t>webapp/auth.py, middleware in app.py</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>suites 08, 10</t>
+          <t>suite 10</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Pages (UI)</t>
+          <t>Runs (RUN)</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>webapp/static/index.html, webapp/inventory.py</t>
+          <t>webapp/app.py (Run, run modes), labportal (RunRegistry), webapp/spokes.py</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>suite 10; screenshots; demo</t>
+          <t>suites 08, 10</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Compliance (CMP)</t>
+          <t>Pages (UI)</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>webapp/app.py (compliance, scheduler, history, metrics), nautobot/golden_config.py</t>
+          <t>webapp/static/index.html, webapp/inventory.py</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>suites 05, 06, 10</t>
+          <t>suite 10; screenshots; demo</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>API (API)</t>
+          <t>Compliance (CMP)</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>webapp/app.py, schemas.py</t>
+          <t>webapp/app.py (compliance, scheduler, history, metrics), nautobot/golden_config.py</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>suite 10, Swagger</t>
+          <t>suites 05, 06, 10</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Monitoring (MON)</t>
+          <t>API (API)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>lab-portal/monitoring/, webapp/app.py (/metrics)</t>
+          <t>webapp/app.py, schemas.py</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>suite 07; Prometheus rules</t>
+          <t>suite 10, Swagger</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
+          <t>Monitoring (MON)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>lab-portal/monitoring/, webapp/app.py (/metrics)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>suite 07; Prometheus rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
           <t>Tests, lab, docs (TST, LAB, DOC)</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>tests/, lab.sh, docs/, webapp/demo/</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>the results directories</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5168,7 +5428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5243,7 +5503,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>VyOS static routes have no description leaf; the breakout uplink uses DHCP on the libvirt NAT network.</t>
+          <t>IOS-XE's CLI RPC rejects a very large payload (bad length/size at roughly two thousand lines): the renderer splits every CLI template into 400-line chunks, repeating the section header. A CLI template never removes the lines of a previous version, so shrinking a scale set means removing the old statements explicitly.</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5513,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Pre-shared keys are kept in the intent (a git-tracked file in the lab); a production deployment would move them to a secret store — the portal already treats them as secrets everywhere else.</t>
+          <t>The Alpine LAN hosts route 10.0.0.0/8 out of their OOB interface, so anything they must reach through the lab is addressed outside that range: the translated ranges live in 100.96.0.0/11 and the acquired company's real prefixes (10.128.0.0/14) are only ever reached through the NAT.</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5523,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Customers are synthetic (deterministic fakes); the model, fields and filters are what a real CRM feed would fill.</t>
+          <t>VyOS static routes have no description leaf; the breakout uplink uses DHCP on the libvirt NAT network.</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5533,32 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
+          <t>Pre-shared keys are kept in the intent (a git-tracked file in the lab); a production deployment would move them to a secret store — the portal already treats them as secrets everywhere else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Customers are synthetic (deterministic fakes); the model, fields and filters are what a real CRM feed would fill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
           <t>Both labs on the host share one Nautobot and one NMS; their test suites must not run concurrently.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Constraints" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$F$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$F$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Roles &amp; glossary'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traceability'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints'!$A$1:$B$12</definedName>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2</v>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>20</v>
@@ -1190,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>Firewalls, Compliance (§16), Audit (§13), Tools (every lab system with URL and login, how to reach each device), the REST API (Swagger / ReDoc) from the navigation.</t>
+          <t>Jobs (#jobs): every run the portal has kept, newest first — what the job does, its target, its status, a progress bar with the step it is on, its duration (ticking while it runs), who started it, the change ticket and the test result; filters by status, by kind of job and a search over router / ticket / user; the list refreshes itself. A job's own page (#job/&lt;id&gt;): what the job does, KPIs (status, steps done, elapsed, who started it, tests passed), every step with its summary and duration, the live log with a follow toggle, the test report with links to the artefacts, Cancel for a queued job and Resume for a failed one. Starting anything anywhere in the portal opens that job's page, and every job id elsewhere links to it.</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>screenshots; suite 07 / 10</t>
+          <t>screenshots; GET /api/runs, GET /api/runs/{id}?since=</t>
         </is>
       </c>
     </row>
@@ -3777,19 +3777,19 @@
           <t>15. Portal: pages</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>Dark mode for the whole portal (CSS tokens; follows the OS setting until chosen; header toggle; remembered per browser).</t>
+          <t>Firewalls, Compliance (§16), Audit (§13), Tools (every lab system with URL and login, how to reach each device), the REST API (Swagger / ReDoc) from the navigation.</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>screenshot portal-dark.png</t>
+          <t>screenshots; suite 07 / 10</t>
         </is>
       </c>
     </row>
@@ -3816,51 +3816,51 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>Every router name anywhere (tables, tunnels, compliance, history) links to its page; Nautobot objects link to Nautobot; the header shows the signed-in user and role.</t>
+          <t>Dark mode for the whole portal (CSS tokens; follows the OS setting until chosen; header toggle; remembered per browser).</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>branchLink()</t>
+          <t>screenshot portal-dark.png</t>
         </is>
       </c>
     </row>
     <row r="83" ht="58" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>CMP-01</t>
+          <t>UI-09</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Compliance and remediation</t>
+          <t>Portal pages</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>15. Portal: pages</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>The Compliance page shows Nautobot Golden Config's verdict: one row per router, one column per feature (✓ / ✕), KPIs (routers and rows compliant, features, last run, schedule), each device's last backup / intended / compliance dates; a cell shows the missing and extra lines, Nautobot's remediation lines and a running-vs-intended diff; non-compliant rows are listed and the first opened.</t>
+          <t>Every router name anywhere (tables, tunnels, compliance, history) links to its page; Nautobot objects link to Nautobot; the header shows the signed-in user and role.</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>GET /api/compliance (cached 30 s, ?refresh); suite 10 "The Compliance page…"</t>
+          <t>branchLink()</t>
         </is>
       </c>
     </row>
     <row r="84" ht="58" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>CMP-02</t>
+          <t>CMP-01</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -3880,19 +3880,19 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>Run Golden Config now (operator): backup every router → render the intended configuration → compliance, nothing pushed; the run fails when any row is non-compliant (so drift is visible as a failed run) and refreshes the report at its end.</t>
+          <t>The Compliance page shows Nautobot Golden Config's verdict: one row per router, one column per feature (✓ / ✕), KPIs (routers and rows compliant, features, last run, schedule), each device's last backup / intended / compliance dates; a cell shows the missing and extra lines, Nautobot's remediation lines and a running-vs-intended diff; non-compliant rows are listed and the first opened.</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>run mode golden; suite 10</t>
+          <t>GET /api/compliance (cached 30 s, ?refresh); suite 10 "The Compliance page…"</t>
         </is>
       </c>
     </row>
     <row r="85" ht="58" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>CMP-03</t>
+          <t>CMP-02</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -3912,19 +3912,19 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>Remediate (operator): for a router's non-compliant features (one, or all), read the verdict again, push the remediation lines Nautobot computed (hier_config: no … for what is extra, the missing lines themselves) in one configuration session, fail on any rejected line, save the configuration, then run Golden Config; refuse a compliant router or a feature without remediation lines.</t>
+          <t>Run Golden Config now (operator): backup every router → render the intended configuration → compliance, nothing pushed; the run fails when any row is non-compliant (so drift is visible as a failed run) and refreshes the report at its end.</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>run mode remediate; suite 10 "Drift on a router is detected…, remediated…"</t>
+          <t>run mode golden; suite 10</t>
         </is>
       </c>
     </row>
     <row r="86" ht="58" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>CMP-04</t>
+          <t>CMP-03</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -3944,19 +3944,19 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>Re-apply from the model (operator): re-assert the model on one router — NaC render → Terraform plan filtered to the router's resources → staged apply targeted at them (skipped when clean) → Golden Config.</t>
+          <t>Remediate (operator): for a router's non-compliant features (one, or all), read the verdict again, push the remediation lines Nautobot computed (hier_config: no … for what is extra, the missing lines themselves) in one configuration session, fail on any rejected line, save the configuration, then run Golden Config; refuse a compliant router or a feature without remediation lines.</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>run mode reapply, nac_apply.py --device; suite 10 "Re-apply from the model restores…"</t>
+          <t>run mode remediate; suite 10 "Drift on a router is detected…, remediated…"</t>
         </is>
       </c>
     </row>
     <row r="87" ht="58" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>CMP-05</t>
+          <t>CMP-04</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -3976,19 +3976,19 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>A scheduled Golden Config run every GOLDEN_INTERVAL_HOURS (default 6; 0 disables), queued as the audited user scheduler, first due one interval after Nautobot's last compliance run (at the earliest two minutes after start-up), skipped and retried while another run is going or the headends are off; interval, next and last run exposed on the page and the API.</t>
+          <t>Re-apply from the model (operator): re-assert the model on one router — NaC render → Terraform plan filtered to the router's resources → staged apply targeted at them (skipped when clean) → Golden Config.</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>golden_schedule(); suite 10 asserts the schedule is enabled and in the future</t>
+          <t>run mode reapply, nac_apply.py --device; suite 10 "Re-apply from the model restores…"</t>
         </is>
       </c>
     </row>
     <row r="88" ht="58" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>CMP-06</t>
+          <t>CMP-05</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -4008,19 +4008,19 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>Drift history: one snapshot per compliance run (per router: compliant, rows, drifted features) appended to compliance-history.jsonl whenever a new compliance date appears; the last 30 shown as dots per router and as a table (which routers drifted, when fixed); per-router series on its page and at GET /api/compliance/history?device=.</t>
+          <t>A scheduled Golden Config run every GOLDEN_INTERVAL_HOURS (default 6; 0 disables), queued as the audited user scheduler, first due one interval after Nautobot's last compliance run (at the earliest two minutes after start-up), skipped and retried while another run is going or the headends are off; interval, next and last run exposed on the page and the API.</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
         <is>
-          <t>suite 10 checks the drift and its repair appear in the history</t>
+          <t>golden_schedule(); suite 10 asserts the schedule is enabled and in the future</t>
         </is>
       </c>
     </row>
     <row r="89" ht="58" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>CMP-07</t>
+          <t>CMP-06</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -4040,19 +4040,19 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>Compliance is exported to Prometheus (lab_config_compliance_ok{device}, lab_config_noncompliant_features, lab_config_compliance_features, lab_config_compliance_last_run_timestamp_seconds, lab_config_compliance_interval_seconds, lab_config_compliance_error) with alerts ConfigDrift (non-compliant 10 min) and ConfigComplianceStale (no run for twice the interval while the lab is up) and a dashboard row.</t>
+          <t>Drift history: one snapshot per compliance run (per router: compliant, rows, drifted features) appended to compliance-history.jsonl whenever a new compliance date appears; the last 30 shown as dots per router and as a table (which routers drifted, when fixed); per-router series on its page and at GET /api/compliance/history?device=.</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>suite 10 reads the metric before and after remediation; lab-portal alerts.yml</t>
+          <t>suite 10 checks the drift and its repair appear in the history</t>
         </is>
       </c>
     </row>
     <row r="90" ht="58" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>CMP-08</t>
+          <t>CMP-07</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -4072,29 +4072,29 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>Terraform-level compliance: after a deploy terraform plan reports no drift from the NaC data model.</t>
+          <t>Compliance is exported to Prometheus (lab_config_compliance_ok{device}, lab_config_noncompliant_features, lab_config_compliance_features, lab_config_compliance_last_run_timestamp_seconds, lab_config_compliance_interval_seconds, lab_config_compliance_error) with alerts ConfigDrift (non-compliant 10 min) and ConfigComplianceStale (no run for twice the interval while the lab is up) and a dashboard row.</t>
         </is>
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>suite 05</t>
+          <t>suite 10 reads the metric before and after remediation; lab-portal alerts.yml</t>
         </is>
       </c>
     </row>
     <row r="91" ht="58" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>API-01</t>
+          <t>CMP-08</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>REST API</t>
+          <t>Compliance and remediation</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>17. REST API</t>
+          <t>16. Configuration compliance, remediation, scheduling and drift history</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -4104,19 +4104,19 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>Everything the UI does is available as a documented REST API (OpenAPI 3.1 at /openapi.json, Swagger UI at /docs, ReDoc at /redoc) with Pydantic schemas and examples; the UI uses nothing else.</t>
+          <t>Terraform-level compliance: after a deploy terraform plan reports no drift from the NaC data model.</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>tags intent, provisioning, runs, inventory, monitoring; suite 10 uses the API throughout</t>
+          <t>suite 05</t>
         </is>
       </c>
     </row>
     <row r="92" ht="58" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>API-02</t>
+          <t>API-01</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -4136,19 +4136,19 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>Endpoints: /api/intent, /api/validate, /api/inventory; /api/spokes/suggest, /api/spokes/validate, /api/hubs/suggest, /api/cities, /api/spokes/{name}/removal|rehome|rotation|auth, /api/routers/{name}/renewal; /api/runs (list, start, get with since, resume, cancel); /api/vpn-inventory[.csv], /api/branches, /api/branch/{name}[/config|/history|/show/{what}], /api/firewalls, /api/hosts, /api/pki, /api/compliance[/history], /api/tools, /api/sd; /api/login|logout|me|oidc*, /api/users, /api/audit; /metrics.</t>
+          <t>Everything the UI does is available as a documented REST API (OpenAPI 3.1 at /openapi.json, Swagger UI at /docs, ReDoc at /redoc) with Pydantic schemas and examples; the UI uses nothing else.</t>
         </is>
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>webapp/app.py</t>
+          <t>tags intent, provisioning, runs, inventory, monitoring; suite 10 uses the API throughout</t>
         </is>
       </c>
     </row>
     <row r="93" ht="58" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>API-03</t>
+          <t>API-02</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -4168,19 +4168,19 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>Errors are explicit: 400 for an unknown mode, 401 / 403 with the required role, 404 for unknown routers / runs, 409 when a run cannot start, 422 with the list of problems for an invalid spec, 502 when a backing system (Gitea, Nautobot) fails.</t>
+          <t>Endpoints: /api/intent, /api/validate, /api/inventory; /api/spokes/suggest, /api/spokes/validate, /api/hubs/suggest, /api/cities, /api/spokes/{name}/removal|rehome|rotation|auth, /api/routers/{name}/renewal; /api/runs (list, start, get with since, resume, cancel); /api/vpn-inventory[.csv], /api/branches, /api/branch/{name}[/config|/history|/show/{what}], /api/firewalls, /api/hosts, /api/pki, /api/compliance[/history], /api/tools, /api/sd; /api/login|logout|me|oidc*, /api/users, /api/audit; /metrics.</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>suite 10 asserts 404 / 422 / 4xx cases</t>
+          <t>webapp/app.py</t>
         </is>
       </c>
     </row>
     <row r="94" ht="58" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>API-04</t>
+          <t>API-03</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -4193,58 +4193,58 @@
           <t>17. REST API</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>Expensive reads are cached with an explicit refresh (inventory live state, firewalls, configuration 60 s, show commands 20 s, compliance 30 s, host mesh 60 s / live 3 s) and report when they were generated.</t>
+          <t>Errors are explicit: 400 for an unknown mode, 401 / 403 with the required role, 404 for unknown routers / runs, 409 when a run cannot start, 422 with the list of problems for an invalid spec, 502 when a backing system (Gitea, Nautobot) fails.</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>generated field on the responses</t>
+          <t>suite 10 asserts 404 / 422 / 4xx cases</t>
         </is>
       </c>
     </row>
     <row r="95" ht="58" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>MON-01</t>
+          <t>API-04</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Monitoring and alerting</t>
+          <t>REST API</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>18. Monitoring, metrics and alerting</t>
-        </is>
-      </c>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>17. REST API</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>The portal exposes /metrics: VMs running per node / role, per-tunnel health (2 up / 1 degraded / 0 down), IKE SA age, BGP prefixes, ESP counters and errors, VTI rates; per-headend tunnels / capacity / free slots / utilisation / CPU / QFP / DRAM / IKE sessions / bandwidth; certificate expiry and authentication per spoke; compliance (§16); run outcomes; collection errors.</t>
+          <t>Expensive reads are cached with an explicit refresh (inventory live state, firewalls, configuration 60 s, show commands 20 s, compliance 30 s, host mesh 60 s / live 3 s) and report when they were generated.</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Prometheus scrapes the portal; dashboard cat8000v-ipsec-overview</t>
+          <t>generated field on the responses</t>
         </is>
       </c>
     </row>
     <row r="96" ht="58" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>MON-02</t>
+          <t>MON-01</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -4264,19 +4264,19 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>Alerts in the shared monitoring: TunnelDown, HeadendUnreachable, HeadendCapacityExhausted, HeadendCpuHigh, InternetBreakoutDown, CertificateExpiringSoon / CertificateExpired, ConfigDrift / ConfigComplianceStale, LabTestsFailed, PortalDown, and from the firewall log FirewallDropBurst / FirewallDroppingPeerTraffic.</t>
+          <t>The portal exposes /metrics: VMs running per node / role, per-tunnel health (2 up / 1 degraded / 0 down), IKE SA age, BGP prefixes, ESP counters and errors, VTI rates; per-headend tunnels / capacity / free slots / utilisation / CPU / QFP / DRAM / IKE sessions / bandwidth; certificate expiry and authentication per spoke; compliance (§16); run outcomes; collection errors.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>lab-portal/monitoring/prometheus/alerts.yml, vmalert/logs-alerts.yml</t>
+          <t>Prometheus scrapes the portal; dashboard cat8000v-ipsec-overview</t>
         </is>
       </c>
     </row>
     <row r="97" ht="58" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>MON-03</t>
+          <t>MON-02</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -4296,19 +4296,19 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>Firewall syslog lands in VictoriaLogs; the dashboard shows drops / accepts per firewall, drops by source, top dropped flows and the raw log; the portal queries the same store for the Firewalls page and a router's page.</t>
+          <t>Alerts in the shared monitoring: TunnelDown, HeadendUnreachable, HeadendCapacityExhausted, HeadendCpuHigh, InternetBreakoutDown, CertificateExpiringSoon / CertificateExpired, ConfigDrift / ConfigComplianceStale, LabTestsFailed, PortalDown, and from the firewall log FirewallDropBurst / FirewallDroppingPeerTraffic.</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>suite 07 "The firewalls ship their firewall log to VictoriaLogs, and the portal…"</t>
+          <t>lab-portal/monitoring/prometheus/alerts.yml, vmalert/logs-alerts.yml</t>
         </is>
       </c>
     </row>
     <row r="98" ht="58" customHeight="1">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>MON-04</t>
+          <t>MON-03</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -4321,58 +4321,58 @@
           <t>18. Monitoring, metrics and alerting</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>Alerts only fire for a running lab (gated on the VM-running metric) so a powered-off lab is a normal state; dashboards are generated from code (gen_dashboards.py) and deployed with one script.</t>
+          <t>Firewall syslog lands in VictoriaLogs; the dashboard shows drops / accepts per firewall, drops by source, top dropped flows and the raw log; the portal queries the same store for the Firewalls page and a router's page.</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>monitoring/deploy.sh</t>
+          <t>suite 07 "The firewalls ship their firewall log to VictoriaLogs, and the portal…"</t>
         </is>
       </c>
     </row>
     <row r="99" ht="58" customHeight="1">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>TST-01</t>
+          <t>MON-04</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Verification (tests)</t>
+          <t>Monitoring and alerting</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>19. Verification: the Robot Framework suites</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>18. Monitoring, metrics and alerting</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet, 12 the DCI chain (incl. the twice-NAT and the DNS fix-up at scale) — 74 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
+          <t>Alerts only fire for a running lab (gated on the VM-running metric) so a powered-off lab is a normal state; dashboards are generated from code (gen_dashboards.py) and deployed with one script.</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>./lab.sh test; tests/resources/lab_vars.py</t>
+          <t>monitoring/deploy.sh</t>
         </is>
       </c>
     </row>
     <row r="100" ht="58" customHeight="1">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>TST-02</t>
+          <t>TST-01</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -4392,19 +4392,19 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>Tests that change the lab do so for real and leave it as found: a renewal, a PSK ↔ certificate switch there and back, injected drift remediated and re-applied, queued runs cancelled — with teardowns.</t>
+          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet, 12 the DCI chain (incl. the twice-NAT and the DNS fix-up at scale) — 74 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>suites 08 and 10</t>
+          <t>./lab.sh test; tests/resources/lab_vars.py</t>
         </is>
       </c>
     </row>
     <row r="101" ht="58" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>TST-03</t>
+          <t>TST-02</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -4424,19 +4424,19 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate. Every run also produces report.pdf — an evidence report built from output.xml (tests/report_pdf.py): every suite and test with its result, its duration and the numbers it measured.</t>
+          <t>Tests that change the lab do so for real and leave it as found: a renewal, a PSK ↔ certificate switch there and back, injected drift remediated and re-applied, queued runs cancelled — with teardowns.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>tests/run.sh, capture_configs.py</t>
+          <t>suites 08 and 10</t>
         </is>
       </c>
     </row>
     <row r="102" ht="58" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>TST-04</t>
+          <t>TST-03</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -4449,58 +4449,58 @@
           <t>19. Verification: the Robot Framework suites</t>
         </is>
       </c>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Tests can be run from the portal (a test run, or at the end of any pipeline) and their report is parsed into the run (suites, tests, pass / fail, elapsed).</t>
+          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate. Every run also produces report.pdf — an evidence report built from output.xml (tests/report_pdf.py): every suite and test with its result, its duration and the numbers it measured.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>parse_robot; Run.tests</t>
+          <t>tests/run.sh, capture_configs.py</t>
         </is>
       </c>
     </row>
     <row r="103" ht="58" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>LAB-01</t>
+          <t>TST-04</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Lab infrastructure</t>
+          <t>Verification (tests)</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>20. Lab infrastructure and operations</t>
-        </is>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>19. Verification: the Robot Framework suites</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>lab.sh is the one operations entry point: up | down | status | console | ssh | bootstrap | wait | log | nac | nautobot (onboard | seed | render | vyos | pki | golden | token) | test | intent | webapp | rename | rebuild | clean | hosts; VMs are libvirt domains generated from lab.conf (node index → MACs, UDP socket links, console ports), with day-0 ISOs, license reload and RESTCONF wait on first boot.</t>
+          <t>Tests can be run from the portal (a test run, or at the end of any pipeline) and their report is parsed into the run (suites, tests, pass / fail, elapsed).</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>README quick start</t>
+          <t>parse_robot; Run.tests</t>
         </is>
       </c>
     </row>
     <row r="104" ht="58" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>LAB-02</t>
+          <t>LAB-01</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -4520,19 +4520,19 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>New routers, firewalls and hosts can be added without editing XML: the portal registers them in lab.conf, writes the day-0 config, defines and boots the VM; a spoke can be re-defined for a new NIC (re-home) and removed with its disk.</t>
+          <t>lab.sh is the one operations entry point: up | down | status | console | ssh | bootstrap | wait | log | nac | nautobot (onboard | seed | render | vyos | pki | golden | token) | test | intent | webapp | rename | rebuild | clean | hosts; VMs are libvirt domains generated from lab.conf (node index → MACs, UDP socket links, console ports), with day-0 ISOs, license reload and RESTCONF wait on first boot.</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>spokes.add_to_lab_conf / write_day0 / destroy_vm</t>
+          <t>README quick start</t>
         </is>
       </c>
     </row>
     <row r="105" ht="58" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>LAB-03</t>
+          <t>LAB-02</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -4545,58 +4545,58 @@
           <t>20. Lab infrastructure and operations</t>
         </is>
       </c>
-      <c r="D105" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>The portal runs as a user systemd service, the monitoring as Docker Compose on the NMS with one deploy script; both labs on the host never run their test suites concurrently.</t>
+          <t>New routers, firewalls and hosts can be added without editing XML: the portal registers them in lab.conf, writes the day-0 config, defines and boots the VM; a spoke can be re-defined for a new NIC (re-home) and removed with its disk.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>lab-webapp.service, monitoring/deploy.sh</t>
+          <t>spokes.add_to_lab_conf / write_day0 / destroy_vm</t>
         </is>
       </c>
     </row>
     <row r="106" ht="58" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>DOC-01</t>
+          <t>LAB-03</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Lab infrastructure</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>21. Documentation and demos</t>
-        </is>
-      </c>
-      <c r="D106" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>20. Lab infrastructure and operations</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>A README describing the topology, quick start, every portal feature with screenshots, the Nautobot model, the pipeline, the test suites and the file map; component READMEs for the portal, Nautobot scripts, NaC, tests and monitoring.</t>
+          <t>The portal runs as a user systemd service, the monitoring as Docker Compose on the NMS with one deploy script; both labs on the host never run their test suites concurrently.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>README.md, webapp/README.md, nautobot/README.md, …</t>
+          <t>lab-webapp.service, monitoring/deploy.sh</t>
         </is>
       </c>
     </row>
     <row r="107" ht="58" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>DOC-02</t>
+          <t>DOC-01</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -4616,29 +4616,29 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>Generated documents kept current from the code: the workflows / data-flow / decision-tree PDF, this requirements specification, the screenshots (docs/screenshots.py) and an annotated demo video of the portal (webapp/demo/record.py, MP4 + GIF) plus a Nautobot / NaC data-flow demo.</t>
+          <t>A README describing the topology, quick start, every portal feature with screenshots, the Nautobot model, the pipeline, the test suites and the file map; component READMEs for the portal, Nautobot scripts, NaC, tests and monitoring.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>docs/workflows.pdf, docs/requirements.pdf, webapp/demo/</t>
+          <t>README.md, webapp/README.md, nautobot/README.md, …</t>
         </is>
       </c>
     </row>
     <row r="108" ht="58" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>NFR-01</t>
+          <t>DOC-02</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>22. Non-functional requirements</t>
+          <t>21. Documentation and demos</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
@@ -4648,19 +4648,19 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Idempotence: seed, render, firewall push, pki and apply can be re-run at any time and change nothing when nothing changed.</t>
+          <t>Generated documents kept current from the code: the workflows / data-flow / decision-tree PDF, this requirements specification, the screenshots (docs/screenshots.py) and an annotated demo video of the portal (webapp/demo/record.py, MP4 + GIF) plus a Nautobot / NaC data-flow demo.</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>seed "0 changes", render --check, vyos --check, pki --check, plan exit code 0</t>
+          <t>docs/workflows.pdf, docs/requirements.pdf, webapp/demo/</t>
         </is>
       </c>
     </row>
     <row r="109" ht="58" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>NFR-02</t>
+          <t>NFR-01</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -4680,19 +4680,19 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>Safety of change: nothing is pushed without a plan; applies are staged; verification steps fail the run rather than leave a half-authenticated tunnel; a run never starts on an invalid spec; runs are serialised.</t>
+          <t>Idempotence: seed, render, firewall push, pki and apply can be re-run at any time and change nothing when nothing changed.</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>§6, §8, §14</t>
+          <t>seed "0 changes", render --check, vyos --check, pki --check, plan exit code 0</t>
         </is>
       </c>
     </row>
     <row r="110" ht="58" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>NFR-03</t>
+          <t>NFR-02</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -4712,19 +4712,19 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>Traceability: every change carries a change ticket, a user and a run id; Nautobot records fingerprints, certificates, dates; Gitea holds every backup; the audit log every action; results directories every test run.</t>
+          <t>Safety of change: nothing is pushed without a plan; applies are staged; verification steps fail the run rather than leave a half-authenticated tunnel; a run never starts on an invalid spec; runs are serialised.</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>§13, §19</t>
+          <t>§6, §8, §14</t>
         </is>
       </c>
     </row>
     <row r="111" ht="58" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>NFR-03</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -4737,26 +4737,26 @@
           <t>22. Non-functional requirements</t>
         </is>
       </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>Responsiveness: pages render from caches within a second; a Golden Config run completes in about 20 s for 7 routers; a remediation in about 30 s; a re-apply in about 2 min; a run that renders, plans and applies the whole model (a spoke provisioning, an authentication switch) in about 12 min with the DCI's scale set in it; the full test suite in about 55 min.</t>
+          <t>Traceability: every change carries a change ticket, a user and a run id; Nautobot records fingerprints, certificates, dates; Gitea holds every backup; the audit log every action; results directories every test run.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>observed run timings in the run records</t>
+          <t>§13, §19</t>
         </is>
       </c>
     </row>
     <row r="112" ht="58" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>NFR-05</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -4776,19 +4776,19 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>Resilience: the portal survives Nautobot / Gitea / headend outages on read paths (errors reported in place, collectors degrade, metrics export an error series); interrupted runs are marked and resumable.</t>
+          <t>Responsiveness: pages render from caches within a second; a Golden Config run completes in about 20 s for 7 routers; a remediation in about 30 s; a re-apply in about 2 min; a run that renders, plans and applies the whole model (a spoke provisioning, an authentication switch) in about 12 min with the DCI's scale set in it; the full test suite in about 55 min.</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>inventory_error, lab_inventory_error, lab_config_compliance_error</t>
+          <t>observed run timings in the run records</t>
         </is>
       </c>
     </row>
     <row r="113" ht="58" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>NFR-06</t>
+          <t>NFR-05</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -4808,49 +4808,81 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>Footprint: LAN hosts are 256 MiB VMs; routers 4 GiB; the whole lab fits one 57 GiB host next to the SRv6 lab and the NMS.</t>
+          <t>Resilience: the portal survives Nautobot / Gitea / headend outages on read paths (errors reported in place, collectors degrade, metrics export an error series); interrupted runs are marked and resumable.</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>memory check in spokes.validate before a VM is created</t>
+          <t>inventory_error, lab_inventory_error, lab_config_compliance_error</t>
         </is>
       </c>
     </row>
     <row r="114" ht="58" customHeight="1">
       <c r="A114" s="10" t="inlineStr">
         <is>
+          <t>NFR-06</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>Footprint: LAN hosts are 256 MiB VMs; routers 4 GiB; the whole lab fits one 57 GiB host next to the SRv6 lab and the NMS.</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>memory check in spokes.validate before a VM is created</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="58" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
           <t>NFR-07</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>22. Non-functional requirements</t>
         </is>
       </c>
-      <c r="D114" s="12" t="inlineStr">
+      <c r="D115" s="12" t="inlineStr">
         <is>
           <t>SHOULD</t>
         </is>
       </c>
-      <c r="E114" s="9" t="inlineStr">
+      <c r="E115" s="9" t="inlineStr">
         <is>
           <t>Usability: every value the wizard needs is suggested; every dialog previews what will change; every table links to the object's page and to Nautobot; dark mode; the UI degrades to the role.</t>
         </is>
       </c>
-      <c r="F114" s="9" t="inlineStr">
+      <c r="F115" s="9" t="inlineStr">
         <is>
           <t>§14, §15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F114"/>
+  <autoFilter ref="A1:F115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -2957,7 +2957,7 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>suite 12 "DNS is fixed up on the way through the NAT…", "DNS fix-up scales and works from either side…"</t>
+          <t>suite 12 "DNS is fixed up on the way through the NAT…", "DNS fix-up scales and works from either side…" and "The fix-up is visible on the wire…" — a packet capture on both of the DCI's interfaces shows the same answer carrying the real address inside and its translated form outside (tools/dns_capture.py, .pcap kept with the run)</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet, 12 the DCI chain (incl. the twice-NAT and the DNS fix-up at scale) — 74 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
+          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet, 12 the DCI chain (incl. the twice-NAT, the DNS fix-up at scale and the packet capture that proves it) — 75 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate. Every run also produces report.pdf — an evidence report built from output.xml (tests/report_pdf.py): every suite and test with its result, its duration and the numbers it measured.</t>
+          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate, together with the .pcap files of the DNS capture. Every run also produces report.pdf — an evidence report built from output.xml (tests/report_pdf.py): every suite and test with its result, its duration and the numbers it measured.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">

--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Constraints" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$F$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$F$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Roles &amp; glossary'!$A$1:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Traceability'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Constraints'!$A$1:$B$12</definedName>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>1</v>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>20</v>
@@ -1190,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4404,7 +4404,7 @@
     <row r="101" ht="58" customHeight="1">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>TST-02</t>
+          <t>TST-05</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -4424,19 +4424,19 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>Tests that change the lab do so for real and leave it as found: a renewal, a PSK ↔ certificate switch there and back, injected drift remediated and re-applied, queued runs cancelled — with teardowns.</t>
+          <t>A suite waits for the portal's run queue before it starts (jobs execute one at a time; a suite started mid-job fails every test that needs the queue) and names the job it is waiting for; the portal's own test step is exempt, and QUEUE_WAIT=0 skips the check. The scheduled Golden Config run skips its cycle while a job is running.</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>suites 08 and 10</t>
+          <t>tests/queue_state.py, tests/run.sh; _golden_scheduler</t>
         </is>
       </c>
     </row>
     <row r="102" ht="58" customHeight="1">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>TST-03</t>
+          <t>TST-02</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -4456,19 +4456,19 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate, together with the .pcap files of the DNS capture. Every run also produces report.pdf — an evidence report built from output.xml (tests/report_pdf.py): every suite and test with its result, its duration and the numbers it measured.</t>
+          <t>Tests that change the lab do so for real and leave it as found: a renewal, a PSK ↔ certificate switch there and back, injected drift remediated and re-applied, queued runs cancelled — with teardowns.</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>tests/run.sh, capture_configs.py</t>
+          <t>suites 08 and 10</t>
         </is>
       </c>
     </row>
     <row r="103" ht="58" customHeight="1">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>TST-04</t>
+          <t>TST-03</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -4481,58 +4481,58 @@
           <t>19. Verification: the Robot Framework suites</t>
         </is>
       </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>Tests can be run from the portal (a test run, or at the end of any pipeline) and their report is parsed into the run (suites, tests, pass / fail, elapsed).</t>
+          <t>Every run keeps pre / post configuration backups of every router and a diff of what the run changed under results/&lt;timestamp&gt;/ with Robot's log and report; results/latest points at the last run; results are committed with the change they validate, together with the .pcap files of the DNS capture. Every run also produces report.pdf — an evidence report built from output.xml (tests/report_pdf.py): every suite and test with its result, its duration and the numbers it measured.</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>parse_robot; Run.tests</t>
+          <t>tests/run.sh, capture_configs.py</t>
         </is>
       </c>
     </row>
     <row r="104" ht="58" customHeight="1">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>LAB-01</t>
+          <t>TST-04</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Lab infrastructure</t>
+          <t>Verification (tests)</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>20. Lab infrastructure and operations</t>
-        </is>
-      </c>
-      <c r="D104" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>19. Verification: the Robot Framework suites</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>lab.sh is the one operations entry point: up | down | status | console | ssh | bootstrap | wait | log | nac | nautobot (onboard | seed | render | vyos | pki | golden | token) | test | intent | webapp | rename | rebuild | clean | hosts; VMs are libvirt domains generated from lab.conf (node index → MACs, UDP socket links, console ports), with day-0 ISOs, license reload and RESTCONF wait on first boot.</t>
+          <t>Tests can be run from the portal (a test run, or at the end of any pipeline) and their report is parsed into the run (suites, tests, pass / fail, elapsed).</t>
         </is>
       </c>
       <c r="F104" s="9" t="inlineStr">
         <is>
-          <t>README quick start</t>
+          <t>parse_robot; Run.tests</t>
         </is>
       </c>
     </row>
     <row r="105" ht="58" customHeight="1">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>LAB-02</t>
+          <t>LAB-01</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -4552,19 +4552,19 @@
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>New routers, firewalls and hosts can be added without editing XML: the portal registers them in lab.conf, writes the day-0 config, defines and boots the VM; a spoke can be re-defined for a new NIC (re-home) and removed with its disk.</t>
+          <t>lab.sh is the one operations entry point: up | down | status | console | ssh | bootstrap | wait | log | nac | nautobot (onboard | seed | render | vyos | pki | golden | token) | test | intent | webapp | rename | rebuild | clean | hosts; VMs are libvirt domains generated from lab.conf (node index → MACs, UDP socket links, console ports), with day-0 ISOs, license reload and RESTCONF wait on first boot.</t>
         </is>
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>spokes.add_to_lab_conf / write_day0 / destroy_vm</t>
+          <t>README quick start</t>
         </is>
       </c>
     </row>
     <row r="106" ht="58" customHeight="1">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>LAB-03</t>
+          <t>LAB-02</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -4577,58 +4577,58 @@
           <t>20. Lab infrastructure and operations</t>
         </is>
       </c>
-      <c r="D106" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>The portal runs as a user systemd service, the monitoring as Docker Compose on the NMS with one deploy script; both labs on the host never run their test suites concurrently.</t>
+          <t>New routers, firewalls and hosts can be added without editing XML: the portal registers them in lab.conf, writes the day-0 config, defines and boots the VM; a spoke can be re-defined for a new NIC (re-home) and removed with its disk.</t>
         </is>
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>lab-webapp.service, monitoring/deploy.sh</t>
+          <t>spokes.add_to_lab_conf / write_day0 / destroy_vm</t>
         </is>
       </c>
     </row>
     <row r="107" ht="58" customHeight="1">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>DOC-01</t>
+          <t>LAB-03</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Lab infrastructure</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>21. Documentation and demos</t>
-        </is>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>MUST</t>
+          <t>20. Lab infrastructure and operations</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
         </is>
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>A README describing the topology, quick start, every portal feature with screenshots, the Nautobot model, the pipeline, the test suites and the file map; component READMEs for the portal, Nautobot scripts, NaC, tests and monitoring.</t>
+          <t>The portal runs as a user systemd service, the monitoring as Docker Compose on the NMS with one deploy script; both labs on the host never run their test suites concurrently.</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>README.md, webapp/README.md, nautobot/README.md, …</t>
+          <t>lab-webapp.service, monitoring/deploy.sh</t>
         </is>
       </c>
     </row>
     <row r="108" ht="58" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>DOC-02</t>
+          <t>DOC-01</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -4648,29 +4648,29 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>Generated documents kept current from the code: the workflows / data-flow / decision-tree PDF, this requirements specification, the screenshots (docs/screenshots.py) and an annotated demo video of the portal (webapp/demo/record.py, MP4 + GIF) plus a Nautobot / NaC data-flow demo.</t>
+          <t>A README describing the topology, quick start, every portal feature with screenshots, the Nautobot model, the pipeline, the test suites and the file map; component READMEs for the portal, Nautobot scripts, NaC, tests and monitoring.</t>
         </is>
       </c>
       <c r="F108" s="9" t="inlineStr">
         <is>
-          <t>docs/workflows.pdf, docs/requirements.pdf, webapp/demo/</t>
+          <t>README.md, webapp/README.md, nautobot/README.md, …</t>
         </is>
       </c>
     </row>
     <row r="109" ht="58" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>NFR-01</t>
+          <t>DOC-02</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>22. Non-functional requirements</t>
+          <t>21. Documentation and demos</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
@@ -4680,19 +4680,19 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>Idempotence: seed, render, firewall push, pki and apply can be re-run at any time and change nothing when nothing changed.</t>
+          <t>Generated documents kept current from the code: the workflows / data-flow / decision-tree PDF, this requirements specification, the screenshots (docs/screenshots.py) and an annotated demo video of the portal (webapp/demo/record.py, MP4 + GIF) plus a Nautobot / NaC data-flow demo.</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>seed "0 changes", render --check, vyos --check, pki --check, plan exit code 0</t>
+          <t>docs/workflows.pdf, docs/requirements.pdf, webapp/demo/</t>
         </is>
       </c>
     </row>
     <row r="110" ht="58" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>NFR-02</t>
+          <t>NFR-01</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -4712,19 +4712,19 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>Safety of change: nothing is pushed without a plan; applies are staged; verification steps fail the run rather than leave a half-authenticated tunnel; a run never starts on an invalid spec; runs are serialised.</t>
+          <t>Idempotence: seed, render, firewall push, pki and apply can be re-run at any time and change nothing when nothing changed.</t>
         </is>
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>§6, §8, §14</t>
+          <t>seed "0 changes", render --check, vyos --check, pki --check, plan exit code 0</t>
         </is>
       </c>
     </row>
     <row r="111" ht="58" customHeight="1">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>NFR-03</t>
+          <t>NFR-02</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -4744,19 +4744,19 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>Traceability: every change carries a change ticket, a user and a run id; Nautobot records fingerprints, certificates, dates; Gitea holds every backup; the audit log every action; results directories every test run.</t>
+          <t>Safety of change: nothing is pushed without a plan; applies are staged; verification steps fail the run rather than leave a half-authenticated tunnel; a run never starts on an invalid spec; runs are serialised.</t>
         </is>
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>§13, §19</t>
+          <t>§6, §8, §14</t>
         </is>
       </c>
     </row>
     <row r="112" ht="58" customHeight="1">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>NFR-03</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -4769,26 +4769,26 @@
           <t>22. Non-functional requirements</t>
         </is>
       </c>
-      <c r="D112" s="12" t="inlineStr">
-        <is>
-          <t>SHOULD</t>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>MUST</t>
         </is>
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>Responsiveness: pages render from caches within a second; a Golden Config run completes in about 20 s for 7 routers; a remediation in about 30 s; a re-apply in about 2 min; a run that renders, plans and applies the whole model (a spoke provisioning, an authentication switch) in about 12 min with the DCI's scale set in it; the full test suite in about 55 min.</t>
+          <t>Traceability: every change carries a change ticket, a user and a run id; Nautobot records fingerprints, certificates, dates; Gitea holds every backup; the audit log every action; results directories every test run.</t>
         </is>
       </c>
       <c r="F112" s="9" t="inlineStr">
         <is>
-          <t>observed run timings in the run records</t>
+          <t>§13, §19</t>
         </is>
       </c>
     </row>
     <row r="113" ht="58" customHeight="1">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>NFR-05</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -4808,19 +4808,19 @@
       </c>
       <c r="E113" s="9" t="inlineStr">
         <is>
-          <t>Resilience: the portal survives Nautobot / Gitea / headend outages on read paths (errors reported in place, collectors degrade, metrics export an error series); interrupted runs are marked and resumable.</t>
+          <t>Responsiveness: pages render from caches within a second; a Golden Config run completes in about 20 s for 7 routers; a remediation in about 30 s; a re-apply in about 2 min; a scoped day-2 job (authentication switch, key rotation, certificate renewal — plans and applies targeted at the branch and its headends) in about 5 min; a job that renders, plans and applies the whole model in about 12 min with the DCI's scale set in it; the full test suite in about 55 min. Plans read in parallel (NAC_PLAN_PARALLELISM), applies stay serial.</t>
         </is>
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>inventory_error, lab_inventory_error, lab_config_compliance_error</t>
+          <t>observed run timings in the run records</t>
         </is>
       </c>
     </row>
     <row r="114" ht="58" customHeight="1">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>NFR-06</t>
+          <t>NFR-05</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -4840,49 +4840,81 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>Footprint: LAN hosts are 256 MiB VMs; routers 4 GiB; the whole lab fits one 57 GiB host next to the SRv6 lab and the NMS.</t>
+          <t>Resilience: the portal survives Nautobot / Gitea / headend outages on read paths (errors reported in place, collectors degrade, metrics export an error series); interrupted runs are marked and resumable.</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>memory check in spokes.validate before a VM is created</t>
+          <t>inventory_error, lab_inventory_error, lab_config_compliance_error</t>
         </is>
       </c>
     </row>
     <row r="115" ht="58" customHeight="1">
       <c r="A115" s="10" t="inlineStr">
         <is>
+          <t>NFR-06</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>22. Non-functional requirements</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>Footprint: LAN hosts are 256 MiB VMs; routers 4 GiB; the whole lab fits one 57 GiB host next to the SRv6 lab and the NMS.</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>memory check in spokes.validate before a VM is created</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="58" customHeight="1">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
           <t>NFR-07</t>
         </is>
       </c>
-      <c r="B115" s="9" t="inlineStr">
+      <c r="B116" s="9" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C115" s="9" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>22. Non-functional requirements</t>
         </is>
       </c>
-      <c r="D115" s="12" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr">
         <is>
           <t>SHOULD</t>
         </is>
       </c>
-      <c r="E115" s="9" t="inlineStr">
+      <c r="E116" s="9" t="inlineStr">
         <is>
           <t>Usability: every value the wizard needs is suggested; every dialog previews what will change; every table links to the object's page and to Nautobot; dark mode; the UI degrades to the role.</t>
         </is>
       </c>
-      <c r="F115" s="9" t="inlineStr">
+      <c r="F116" s="9" t="inlineStr">
         <is>
           <t>§14, §15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F115"/>
+  <autoFilter ref="A1:F116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>The portal exposes /metrics: VMs running per node / role, per-tunnel health (2 up / 1 degraded / 0 down), IKE SA age, BGP prefixes, ESP counters and errors, VTI rates; per-headend tunnels / capacity / free slots / utilisation / CPU / QFP / DRAM / IKE sessions / bandwidth; certificate expiry and authentication per spoke; compliance (§16); run outcomes; collection errors.</t>
+          <t>The portal exposes /metrics: VMs running per node / role, per-tunnel health (2 up / 1 degraded / 0 down), IKE SA age, BGP prefixes, ESP counters and errors, VTI rates; per-headend tunnels / capacity / free slots / utilisation / CPU / QFP / DRAM / IKE sessions / bandwidth; certificate expiry and authentication per spoke; compliance (§16); the interconnect (static translations on the DCI against the model, the NAT table, drops per direction, the aggregates' presence in the routing table, records per DNS zone and the packet-capture verdict of the DNS fix-up); run outcomes; collection errors. The live collectors run in background threads — a scrape is a cache read, never an SSH session.</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">

--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -1453,7 +1453,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>capacity modelled in Nautobot, enforced by spokes.validate_links, shown on the Inventory page; suites 07 and 10</t>
+          <t>capacity modelled in Nautobot, enforced by spokes.validate_links, shown on the Home page; suites 07 and 10</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>The Inventory page shows the mesh green / red with a live mode (one probe per pair every 5 s, round-trip time in the cell) and columns for the router itself and the internet.</t>
+          <t>The Home page shows the mesh green / red with a live mode (one probe per pair every 5 s, round-trip time in the cell) and columns for the router itself and the internet.</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Inventory: KPIs (Nautobot's VPN model joined with live IKEv2 / VTI / eBGP / ESP state from the headends), a rendered topology (headends on top, spokes below, one line per tunnel coloured by health, hover for details, click to open in Nautobot) and a map of the sites, headend capacity (tunnels, bandwidth, CPU / QFP / DRAM, the binding constraint), the per-tunnel report with CSV export, the LAN hosts and their ping mesh.</t>
+          <t>Home (the landing page; #home, and the older #inventory still resolves): KPIs (Nautobot's VPN model joined with live IKEv2 / VTI / eBGP / ESP state from the headends), a rendered topology (headends on top, spokes below, one line per tunnel coloured by health, hover for details, click to open in Nautobot) and a map of the sites, headend capacity (tunnels, bandwidth, CPU / QFP / DRAM, the binding constraint), the per-tunnel report with CSV export, the LAN hosts and their ping mesh.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">

--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -3592,7 +3592,7 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>Provision: the intent as a form (site, service, profile, crypto, PSK policy, internet breakout, capacity); the routers table with role, region, site, AS, router-id, LAN, IKE method, PSK (operators), certificate days left, comments, and the day-2 actions (Change auth, Rotate PSK, Renew cert, Re-home, Remove); Add spoke / Add headend wizards; Deploy / Dry run / Run tests; the run status panel (steps, log, test report) and the recent runs list.</t>
+          <t>Provision: opens on a task launcher — one card per operation (add a branch, add a headend, change IKE authentication, rotate a key, renew a certificate, re-home, remove, deploy, dry run, test, edit the model, check for drift, see the jobs), grouped, each with what it does and how long it takes, greyed with the reason when the role or the lab makes it impossible; the ones that act on one router ask which, offering only those that qualify with the fact that decides it. Below it, the intent as a form (site, service, profile, crypto, PSK policy, internet breakout, capacity); the routers table with role, region, site, AS, router-id, LAN, IKE method, PSK (operators), certificate days left, comments, and the day-2 actions (Change auth, Rotate PSK, Renew cert, Re-home, Remove); Add spoke / Add headend wizards (the headend's identity and the branches to link are suggested); Deploy / Dry run / Run tests; the run status panel (steps, log, test report) and the recent runs list.</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">

--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>The Home page shows the mesh green / red with a live mode (one probe per pair every 5 s, round-trip time in the cell) and columns for the router itself and the internet.</t>
+          <t>The Inventory page shows the mesh green / red with a live mode (one probe per pair every 5 s, round-trip time in the cell) and columns for the router itself and the internet.</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>Home (the landing page; #home, and the older #inventory still resolves): KPIs (Nautobot's VPN model joined with live IKEv2 / VTI / eBGP / ESP state from the headends), a rendered topology (headends on top, spokes below, one line per tunnel coloured by health, hover for details, click to open in Nautobot) and a map of the sites, headend capacity (tunnels, bandwidth, CPU / QFP / DRAM, the binding constraint), the per-tunnel report with CSV export, the LAN hosts and their ping mesh.</t>
+          <t>Home (the landing page, #home): KPIs (Nautobot's VPN model joined with live IKEv2 / VTI / eBGP / ESP state from the headends), a rendered topology (headends on top, spokes below, one line per tunnel coloured by health, hover for details, click to open in Nautobot) and a map of the sites, and headend capacity (tunnels, bandwidth, CPU / QFP / DRAM, the binding constraint).</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>Branches: every branch and headend with customer / owner, site and address, design pattern, tier, AS, LAN, VM state, tunnels up, IKE method, certificate, LAN host, free slots, last run; the filter bar of CUST-04; rows open the router's page.</t>
+          <t>Inventory (#inventory, the older #branches still resolves): every node of the lab — headends, customer branches, the DCI chain, the VyOS firewalls and the Alpine LAN hosts — with customer / owner, site and address, design pattern, tier, AS, address, VM state, tunnels up, IKE method, certificate, what it is attached to, free slots and last run; the filter bar of CUST-04 plus a kind filter; a router's row opens its page, a firewall's the Firewalls page, a host's its router's. The same page carries the per-tunnel report (with CSV export) and the LAN hosts with their ping mesh.</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">

--- a/docs/requirements.xlsx
+++ b/docs/requirements.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>1.0 — 2026-09-22 — derived from the delivered system: every requirement below is implemented and, where stated, verified by the Robot Framework suites (60 tests in 11 suites)</t>
+          <t>1.1 — 2026-09-25 — derived from the delivered system: every requirement below is implemented and, where stated, verified by the Robot Framework suites (74 tests in 12 suites; last full run 68 passed, 0 failed, 6 skipped — the skips are the certificate-mode and portal cases that need a specific starting state)</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet, 12 the DCI chain (incl. the twice-NAT, the DNS fix-up at scale and the packet capture that proves it) — 75 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
+          <t>The whole service is proven by tests against the live lab: 01 management, 02 underlay, 03 IPsec VTI, 04 routing, 05 NaC compliance, 06 Nautobot model, 07 firewalls, 08 PKI, 09 hosts, 10 portal, 11 internet, 12 the DCI chain (incl. the twice-NAT, the DNS fix-up at scale and the packet capture that proves it) — 74 tests; every test reads the expected values from the intent / Nautobot, never from constants.</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
